--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -15,6 +15,7 @@
     <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8600,4 +8601,667 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECRET SHOPPER SCORES — SEPTEMBER 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Meal Period</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Enthusiasm</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Return</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Recommend</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Exceptional Act?</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>INDIVIDUAL PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="23">
+        <f>IFERROR(AVERAGE(C12:C12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Kasey Wilson</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="23">
+        <f>IFERROR(AVERAGE(C13:C13),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="23">
+        <f>IFERROR(AVERAGE(C14:C14),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Ailen Gonzalez Cardero</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="23">
+        <f>IFERROR(AVERAGE(C15:C15),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="23">
+        <f>IFERROR(AVERAGE(C16:C16),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="23">
+        <f>IFERROR(AVERAGE(C17:C17),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="23">
+        <f>IFERROR(AVERAGE(C18:C18),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Brianna Gatewood</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="23">
+        <f>IFERROR(AVERAGE(C19:C19),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>DaKayla Dorsey</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="23">
+        <f>IFERROR(AVERAGE(C20:C20),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="23">
+        <f>IFERROR(AVERAGE(C21:C21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="23">
+        <f>IFERROR(AVERAGE(C22:C22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="23">
+        <f>IFERROR(AVERAGE(C23:C23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="23">
+        <f>IFERROR(AVERAGE(C24:C24),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="23">
+        <f>IFERROR(AVERAGE(C25:C25),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="23">
+        <f>IFERROR(AVERAGE(C26:C26),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Kable</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="23">
+        <f>IFERROR(AVERAGE(C27:C27),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Kaisha Brewer</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="23">
+        <f>IFERROR(AVERAGE(C28:C28),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Kayla Valenzuela</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="23">
+        <f>IFERROR(AVERAGE(C29:C29),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="23">
+        <f>IFERROR(AVERAGE(C30:C30),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="23">
+        <f>IFERROR(AVERAGE(C31:C31),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="23">
+        <f>IFERROR(AVERAGE(C32:C32),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="23">
+        <f>IFERROR(AVERAGE(C33:C33),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="23">
+        <f>IFERROR(AVERAGE(C34:C34),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="23">
+        <f>IFERROR(AVERAGE(C35:C35),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="23">
+        <f>IFERROR(AVERAGE(C36:C36),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="23">
+        <f>IFERROR(AVERAGE(C37:C37),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="23">
+        <f>IFERROR(AVERAGE(C38:C38),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:B11"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -8609,14 +8609,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8636,10 +8637,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -8657,8 +8663,13 @@
           <t>09/14</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>09/22</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -8672,8 +8683,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -8685,8 +8701,11 @@
       <c r="C5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="9" t="inlineStr"/>
+      <c r="D5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -8698,6 +8717,7 @@
       <c r="C6" s="17" t="n"/>
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -8709,6 +8729,7 @@
       <c r="C7" s="17" t="n"/>
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -8720,6 +8741,7 @@
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -8731,6 +8753,7 @@
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -8742,6 +8765,7 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -8750,12 +8774,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -8773,11 +8798,12 @@
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="23">
-        <f>IFERROR(AVERAGE(C12:C12),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="23">
+        <f>IFERROR(AVERAGE(C12:D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -8791,11 +8817,12 @@
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
-      <c r="D13" s="23">
-        <f>IFERROR(AVERAGE(C13:C13),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="23">
+        <f>IFERROR(AVERAGE(C13:D13),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -8809,11 +8836,12 @@
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="23">
-        <f>IFERROR(AVERAGE(C14:C14),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="23">
+        <f>IFERROR(AVERAGE(C14:D14),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -8827,11 +8855,12 @@
         </is>
       </c>
       <c r="C15" s="28" t="n"/>
-      <c r="D15" s="23">
-        <f>IFERROR(AVERAGE(C15:C15),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="23">
+        <f>IFERROR(AVERAGE(C15:D15),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -8845,11 +8874,12 @@
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
-      <c r="D16" s="23">
-        <f>IFERROR(AVERAGE(C16:C16),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="23">
+        <f>IFERROR(AVERAGE(C16:D16),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -8863,11 +8893,12 @@
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
-      <c r="D17" s="23">
-        <f>IFERROR(AVERAGE(C17:C17),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="23">
+        <f>IFERROR(AVERAGE(C17:D17),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -8881,11 +8912,12 @@
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
-      <c r="D18" s="23">
-        <f>IFERROR(AVERAGE(C18:C18),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="23">
+        <f>IFERROR(AVERAGE(C18:D18),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -8899,11 +8931,12 @@
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="23">
-        <f>IFERROR(AVERAGE(C19:C19),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="23">
+        <f>IFERROR(AVERAGE(C19:D19),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -8917,11 +8950,12 @@
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="23">
-        <f>IFERROR(AVERAGE(C20:C20),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="23">
+        <f>IFERROR(AVERAGE(C20:D20),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -8935,11 +8969,12 @@
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="23">
-        <f>IFERROR(AVERAGE(C21:C21),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="23">
+        <f>IFERROR(AVERAGE(C21:D21),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8953,11 +8988,12 @@
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
-      <c r="D22" s="23">
-        <f>IFERROR(AVERAGE(C22:C22),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="23">
+        <f>IFERROR(AVERAGE(C22:D22),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8971,11 +9007,12 @@
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
-      <c r="D23" s="23">
-        <f>IFERROR(AVERAGE(C23:C23),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="23">
+        <f>IFERROR(AVERAGE(C23:D23),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -8989,11 +9026,12 @@
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
-      <c r="D24" s="23">
-        <f>IFERROR(AVERAGE(C24:C24),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="23">
+        <f>IFERROR(AVERAGE(C24:D24),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -9007,11 +9045,12 @@
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
-      <c r="D25" s="23">
-        <f>IFERROR(AVERAGE(C25:C25),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="23">
+        <f>IFERROR(AVERAGE(C25:D25),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -9025,11 +9064,12 @@
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
-      <c r="D26" s="23">
-        <f>IFERROR(AVERAGE(C26:C26),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="23">
+        <f>IFERROR(AVERAGE(C26:D26),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -9043,11 +9083,12 @@
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
-      <c r="D27" s="23">
-        <f>IFERROR(AVERAGE(C27:C27),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="23">
+        <f>IFERROR(AVERAGE(C27:D27),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -9061,11 +9102,12 @@
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="23">
-        <f>IFERROR(AVERAGE(C28:C28),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="23">
+        <f>IFERROR(AVERAGE(C28:D28),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -9079,11 +9121,12 @@
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
-      <c r="D29" s="23">
-        <f>IFERROR(AVERAGE(C29:C29),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="23">
+        <f>IFERROR(AVERAGE(C29:D29),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -9097,11 +9140,12 @@
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="23">
-        <f>IFERROR(AVERAGE(C30:C30),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="23">
+        <f>IFERROR(AVERAGE(C30:D30),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -9115,11 +9159,16 @@
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="23">
-        <f>IFERROR(AVERAGE(C31:C31),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="28" t="n"/>
+      <c r="D31" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" s="23">
+        <f>IFERROR(AVERAGE(C31:D31),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -9133,11 +9182,12 @@
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="23">
-        <f>IFERROR(AVERAGE(C32:C32),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="23">
+        <f>IFERROR(AVERAGE(C32:D32),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -9151,11 +9201,12 @@
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="23">
-        <f>IFERROR(AVERAGE(C33:C33),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="23">
+        <f>IFERROR(AVERAGE(C33:D33),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -9169,11 +9220,12 @@
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
-      <c r="D34" s="23">
-        <f>IFERROR(AVERAGE(C34:C34),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="23">
+        <f>IFERROR(AVERAGE(C34:D34),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -9187,11 +9239,12 @@
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="23">
-        <f>IFERROR(AVERAGE(C35:C35),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="23">
+        <f>IFERROR(AVERAGE(C35:D35),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -9205,11 +9258,12 @@
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="23">
-        <f>IFERROR(AVERAGE(C36:C36),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="23">
+        <f>IFERROR(AVERAGE(C36:D36),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -9223,11 +9277,12 @@
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="23">
-        <f>IFERROR(AVERAGE(C37:C37),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="23">
+        <f>IFERROR(AVERAGE(C37:D37),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -9241,11 +9296,12 @@
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="23">
-        <f>IFERROR(AVERAGE(C38:C38),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="23">
+        <f>IFERROR(AVERAGE(C38:D38),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="28" t="n"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
@@ -9256,9 +9312,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -324,10 +324,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1054,26 +1054,22 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G12" s="21" t="n"/>
       <c r="H12" s="21" t="n"/>
       <c r="I12" s="21" t="n"/>
       <c r="J12" s="21" t="n"/>
-      <c r="K12" s="23">
+      <c r="K12" s="22">
         <f>IFERROR(AVERAGE(C12:J12),"")</f>
         <v/>
       </c>
-      <c r="L12" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -1083,24 +1079,26 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
+          <t>Vicki Lucey</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
+      <c r="G13" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H13" s="21" t="n"/>
       <c r="I13" s="21" t="n"/>
       <c r="J13" s="21" t="n"/>
-      <c r="K13" s="23">
+      <c r="K13" s="22">
         <f>IFERROR(AVERAGE(C13:J13),"")</f>
         <v/>
       </c>
-      <c r="L13" s="21" t="n"/>
+      <c r="L13" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -1110,47 +1108,49 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
+      <c r="D14" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
       <c r="H14" s="21" t="n"/>
       <c r="I14" s="21" t="n"/>
       <c r="J14" s="21" t="n"/>
-      <c r="K14" s="23">
+      <c r="K14" s="22">
         <f>IFERROR(AVERAGE(C14:J14),"")</f>
         <v/>
       </c>
       <c r="L14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="28" t="n"/>
-      <c r="K15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="22">
         <f>IFERROR(AVERAGE(C15:J15),"")</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="n"/>
+      <c r="L15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -1171,7 +1171,7 @@
       <c r="H16" s="28" t="n"/>
       <c r="I16" s="28" t="n"/>
       <c r="J16" s="28" t="n"/>
-      <c r="K16" s="23">
+      <c r="K16" s="22">
         <f>IFERROR(AVERAGE(C16:J16),"")</f>
         <v/>
       </c>
@@ -1185,30 +1185,22 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
-        </is>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>92</v>
-      </c>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
-      <c r="H17" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="H17" s="28" t="n"/>
       <c r="I17" s="28" t="n"/>
       <c r="J17" s="28" t="n"/>
-      <c r="K17" s="23">
+      <c r="K17" s="22">
         <f>IFERROR(AVERAGE(C17:J17),"")</f>
         <v/>
       </c>
-      <c r="L17" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="L17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -1218,22 +1210,24 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="n"/>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="D18" s="28" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="E18" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="I18" s="28" t="n"/>
       <c r="J18" s="28" t="n"/>
-      <c r="K18" s="23">
+      <c r="K18" s="22">
         <f>IFERROR(AVERAGE(C18:J18),"")</f>
         <v/>
       </c>
@@ -1249,7 +1243,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
@@ -1257,12 +1251,14 @@
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="I19" s="28" t="n"/>
+      <c r="I19" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="J19" s="28" t="n"/>
-      <c r="K19" s="23">
+      <c r="K19" s="22">
         <f>IFERROR(AVERAGE(C19:J19),"")</f>
         <v/>
       </c>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -1286,14 +1282,18 @@
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
-      <c r="H20" s="28" t="n"/>
+      <c r="H20" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I20" s="28" t="n"/>
       <c r="J20" s="28" t="n"/>
-      <c r="K20" s="23">
+      <c r="K20" s="22">
         <f>IFERROR(AVERAGE(C20:J20),"")</f>
         <v/>
       </c>
-      <c r="L20" s="28" t="n"/>
+      <c r="L20" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -1314,7 +1314,7 @@
       <c r="H21" s="28" t="n"/>
       <c r="I21" s="28" t="n"/>
       <c r="J21" s="28" t="n"/>
-      <c r="K21" s="23">
+      <c r="K21" s="22">
         <f>IFERROR(AVERAGE(C21:J21),"")</f>
         <v/>
       </c>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -1339,7 +1339,7 @@
       <c r="H22" s="28" t="n"/>
       <c r="I22" s="28" t="n"/>
       <c r="J22" s="28" t="n"/>
-      <c r="K22" s="23">
+      <c r="K22" s="22">
         <f>IFERROR(AVERAGE(C22:J22),"")</f>
         <v/>
       </c>
@@ -1353,34 +1353,22 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>0</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G23" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
       <c r="H23" s="28" t="n"/>
       <c r="I23" s="28" t="n"/>
-      <c r="J23" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="K23" s="23">
+      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="22">
         <f>IFERROR(AVERAGE(C23:J23),"")</f>
         <v/>
       </c>
-      <c r="L23" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -1390,7 +1378,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -1401,7 +1389,7 @@
       <c r="H24" s="28" t="n"/>
       <c r="I24" s="28" t="n"/>
       <c r="J24" s="28" t="n"/>
-      <c r="K24" s="23">
+      <c r="K24" s="22">
         <f>IFERROR(AVERAGE(C24:J24),"")</f>
         <v/>
       </c>
@@ -1415,20 +1403,18 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
-      <c r="D25" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
       <c r="I25" s="28" t="n"/>
       <c r="J25" s="28" t="n"/>
-      <c r="K25" s="23">
+      <c r="K25" s="22">
         <f>IFERROR(AVERAGE(C25:J25),"")</f>
         <v/>
       </c>
@@ -1442,32 +1428,22 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F26" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
       <c r="H26" s="28" t="n"/>
       <c r="I26" s="28" t="n"/>
-      <c r="J26" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="K26" s="23">
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="22">
         <f>IFERROR(AVERAGE(C26:J26),"")</f>
         <v/>
       </c>
-      <c r="L26" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -1477,7 +1453,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -1488,7 +1464,7 @@
       <c r="H27" s="28" t="n"/>
       <c r="I27" s="28" t="n"/>
       <c r="J27" s="28" t="n"/>
-      <c r="K27" s="23">
+      <c r="K27" s="22">
         <f>IFERROR(AVERAGE(C27:J27),"")</f>
         <v/>
       </c>
@@ -1502,22 +1478,34 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
+      <c r="F28" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H28" s="28" t="n"/>
       <c r="I28" s="28" t="n"/>
-      <c r="J28" s="28" t="n"/>
-      <c r="K28" s="23">
+      <c r="J28" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="K28" s="22">
         <f>IFERROR(AVERAGE(C28:J28),"")</f>
         <v/>
       </c>
-      <c r="L28" s="28" t="n"/>
+      <c r="L28" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -1527,7 +1515,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -1538,7 +1526,7 @@
       <c r="H29" s="28" t="n"/>
       <c r="I29" s="28" t="n"/>
       <c r="J29" s="28" t="n"/>
-      <c r="K29" s="23">
+      <c r="K29" s="22">
         <f>IFERROR(AVERAGE(C29:J29),"")</f>
         <v/>
       </c>
@@ -1552,7 +1540,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -1563,7 +1551,7 @@
       <c r="H30" s="28" t="n"/>
       <c r="I30" s="28" t="n"/>
       <c r="J30" s="28" t="n"/>
-      <c r="K30" s="23">
+      <c r="K30" s="22">
         <f>IFERROR(AVERAGE(C30:J30),"")</f>
         <v/>
       </c>
@@ -1577,30 +1565,24 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="D31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
-      <c r="G31" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G31" s="28" t="n"/>
       <c r="H31" s="28" t="n"/>
       <c r="I31" s="28" t="n"/>
-      <c r="J31" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="K31" s="23">
+      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="22">
         <f>IFERROR(AVERAGE(C31:J31),"")</f>
         <v/>
       </c>
-      <c r="L31" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -1610,32 +1592,22 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
-      <c r="I32" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="I32" s="28" t="n"/>
       <c r="J32" s="28" t="n"/>
-      <c r="K32" s="23">
+      <c r="K32" s="22">
         <f>IFERROR(AVERAGE(C32:J32),"")</f>
         <v/>
       </c>
-      <c r="L32" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -1645,12 +1617,10 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="n">
-        <v>92</v>
-      </c>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="30" t="n">
         <v>80</v>
@@ -1658,19 +1628,21 @@
       <c r="F33" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="G33" s="28" t="n"/>
+      <c r="G33" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H33" s="28" t="n"/>
-      <c r="I33" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="I33" s="28" t="n"/>
       <c r="J33" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="K33" s="23">
+      <c r="K33" s="22">
         <f>IFERROR(AVERAGE(C33:J33),"")</f>
         <v/>
       </c>
-      <c r="L33" s="28" t="n"/>
+      <c r="L33" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -1680,7 +1652,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -1691,7 +1663,7 @@
       <c r="H34" s="28" t="n"/>
       <c r="I34" s="28" t="n"/>
       <c r="J34" s="28" t="n"/>
-      <c r="K34" s="23">
+      <c r="K34" s="22">
         <f>IFERROR(AVERAGE(C34:J34),"")</f>
         <v/>
       </c>
@@ -1705,7 +1677,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -1716,7 +1688,7 @@
       <c r="H35" s="28" t="n"/>
       <c r="I35" s="28" t="n"/>
       <c r="J35" s="28" t="n"/>
-      <c r="K35" s="23">
+      <c r="K35" s="22">
         <f>IFERROR(AVERAGE(C35:J35),"")</f>
         <v/>
       </c>
@@ -1730,7 +1702,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -1741,7 +1713,7 @@
       <c r="H36" s="28" t="n"/>
       <c r="I36" s="28" t="n"/>
       <c r="J36" s="28" t="n"/>
-      <c r="K36" s="23">
+      <c r="K36" s="22">
         <f>IFERROR(AVERAGE(C36:J36),"")</f>
         <v/>
       </c>
@@ -1755,32 +1727,22 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
-      <c r="H37" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="28" t="n"/>
       <c r="J37" s="28" t="n"/>
-      <c r="K37" s="23">
+      <c r="K37" s="22">
         <f>IFERROR(AVERAGE(C37:J37),"")</f>
         <v/>
       </c>
-      <c r="L37" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="L37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -1790,25 +1752,377 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="E38" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
+      <c r="G38" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H38" s="28" t="n"/>
       <c r="I38" s="28" t="n"/>
-      <c r="J38" s="28" t="n"/>
-      <c r="K38" s="23">
+      <c r="J38" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="K38" s="22">
         <f>IFERROR(AVERAGE(C38:J38),"")</f>
         <v/>
       </c>
-      <c r="L38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="L38" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="28" t="n"/>
+      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="22">
+        <f>IFERROR(AVERAGE(C39:J39),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="K40" s="22">
+        <f>IFERROR(AVERAGE(C40:J40),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="24" t="n">
+        <v>84.33</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J41" s="28" t="n"/>
+      <c r="K41" s="22">
+        <f>IFERROR(AVERAGE(C41:J41),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="K42" s="22">
+        <f>IFERROR(AVERAGE(C42:J42),"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="28" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="22">
+        <f>IFERROR(AVERAGE(C43:J43),"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="28" t="n"/>
+      <c r="J44" s="28" t="n"/>
+      <c r="K44" s="22">
+        <f>IFERROR(AVERAGE(C44:J44),"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="28" t="n"/>
+      <c r="J45" s="28" t="n"/>
+      <c r="K45" s="22">
+        <f>IFERROR(AVERAGE(C45:J45),"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="28" t="n"/>
+      <c r="J46" s="28" t="n"/>
+      <c r="K46" s="22">
+        <f>IFERROR(AVERAGE(C46:J46),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="28" t="n"/>
+      <c r="J47" s="28" t="n"/>
+      <c r="K47" s="22">
+        <f>IFERROR(AVERAGE(C47:J47),"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I48" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J48" s="28" t="n"/>
+      <c r="K48" s="22">
+        <f>IFERROR(AVERAGE(C48:J48),"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="28" t="n"/>
+      <c r="J49" s="28" t="n"/>
+      <c r="K49" s="22">
+        <f>IFERROR(AVERAGE(C49:J49),"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="28" t="n"/>
+      <c r="J50" s="28" t="n"/>
+      <c r="K50" s="22">
+        <f>IFERROR(AVERAGE(C50:J50),"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -1816,7 +2130,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -1832,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2117,26 +2431,20 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
-      <c r="E12" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G12" s="21" t="n"/>
       <c r="H12" s="21" t="n"/>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
-      <c r="J12" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -2146,20 +2454,20 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
+          <t>Vicki Lucey</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="22" t="n">
+      <c r="E13" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="I13" s="23">
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
@@ -2175,43 +2483,49 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
+      <c r="F14" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="23">
+      <c r="H14" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="I14" s="22">
         <f>IFERROR(AVERAGE(C14:H14),"")</f>
         <v/>
       </c>
-      <c r="J14" s="21" t="n"/>
+      <c r="J14" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -2221,7 +2535,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -2230,7 +2544,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -2244,7 +2558,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
@@ -2253,7 +2567,7 @@
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
@@ -2267,7 +2581,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
@@ -2275,10 +2589,8 @@
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="I18" s="23">
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
@@ -2292,7 +2604,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
@@ -2300,8 +2612,10 @@
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="23">
+      <c r="H19" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
@@ -2315,7 +2629,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -2324,7 +2638,7 @@
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
@@ -2338,7 +2652,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -2347,7 +2661,7 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
@@ -2361,7 +2675,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -2370,7 +2684,7 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
@@ -2384,28 +2698,20 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E23" s="28" t="n"/>
       <c r="F23" s="28" t="n"/>
-      <c r="G23" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G23" s="28" t="n"/>
       <c r="H23" s="28" t="n"/>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -2415,7 +2721,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -2424,7 +2730,7 @@
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
@@ -2438,26 +2744,20 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
-      <c r="H25" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="I25" s="23">
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
-      <c r="J25" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -2467,30 +2767,20 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="I26" s="23">
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
-      <c r="J26" s="24" t="n">
-        <v>122.67</v>
-      </c>
+      <c r="J26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -2500,7 +2790,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -2509,7 +2799,7 @@
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
@@ -2523,20 +2813,28 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="E28" s="25" t="n">
+        <v>69</v>
+      </c>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
+      <c r="G28" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
-      <c r="J28" s="28" t="n"/>
+      <c r="J28" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -2546,7 +2844,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -2555,7 +2853,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -2569,7 +2867,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -2578,7 +2876,7 @@
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
@@ -2592,27 +2890,25 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="28" t="n"/>
-      <c r="I31" s="23">
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="24" t="n">
-        <v>84.33</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
@@ -2623,30 +2919,20 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="24" t="n">
-        <v>153.33</v>
-      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -2656,29 +2942,29 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="n">
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
         <v>100</v>
       </c>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="22" t="n">
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="23" t="n">
         <v>100</v>
       </c>
       <c r="H33" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="24" t="n">
-        <v>84.33</v>
+        <v>122.67</v>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
@@ -2689,7 +2975,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -2698,7 +2984,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -2712,7 +2998,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -2721,7 +3007,7 @@
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
@@ -2735,7 +3021,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -2744,7 +3030,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -2758,26 +3044,20 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
-      <c r="J37" s="24" t="n">
-        <v>115</v>
-      </c>
+      <c r="J37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -2787,23 +3067,343 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="22">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>84.33</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>153.33</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>84.33</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="24" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
           <t>Zack Whitten</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
-        <f>IFERROR(AVERAGE(C38:H38),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -2811,9 +3411,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2827,7 +3427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3087,25 +3687,19 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
-      <c r="E12" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" s="23">
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="22">
         <f>IFERROR(AVERAGE(C12:G12),"")</f>
         <v/>
       </c>
-      <c r="I12" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -3115,23 +3709,25 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
-        </is>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="25" t="n">
         <v>72</v>
       </c>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="23">
+      <c r="G13" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" s="22">
         <f>IFERROR(AVERAGE(C13:G13),"")</f>
         <v/>
       </c>
-      <c r="I13" s="21" t="n"/>
+      <c r="I13" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -3141,45 +3737,49 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
+          <t>Kasey Wilson</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="22">
+        <f>IFERROR(AVERAGE(C14:G14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
           <t>Nathan Roberts</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="22" t="n">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="23">
-        <f>IFERROR(AVERAGE(C14:G14),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="24" t="n">
+      <c r="H15" s="22">
+        <f>IFERROR(AVERAGE(C15:G15),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="24" t="n">
         <v>38.33</v>
       </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="23">
-        <f>IFERROR(AVERAGE(C15:G15),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="28" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -3189,7 +3789,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -3197,7 +3797,7 @@
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <f>IFERROR(AVERAGE(C16:G16),"")</f>
         <v/>
       </c>
@@ -3211,7 +3811,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
@@ -3219,7 +3819,7 @@
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <f>IFERROR(AVERAGE(C17:G17),"")</f>
         <v/>
       </c>
@@ -3233,19 +3833,15 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="25" t="n">
-        <v>49</v>
-      </c>
+      <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <f>IFERROR(AVERAGE(C18:G18),"")</f>
         <v/>
       </c>
@@ -3259,17 +3855,19 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="n"/>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="D19" s="28" t="n"/>
-      <c r="E19" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="F19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="25" t="n">
+        <v>49</v>
+      </c>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <f>IFERROR(AVERAGE(C19:G19),"")</f>
         <v/>
       </c>
@@ -3283,15 +3881,17 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="E20" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <f>IFERROR(AVERAGE(C20:G20),"")</f>
         <v/>
       </c>
@@ -3305,7 +3905,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -3313,7 +3913,7 @@
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <f>IFERROR(AVERAGE(C21:G21),"")</f>
         <v/>
       </c>
@@ -3327,7 +3927,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -3335,7 +3935,7 @@
       <c r="E22" s="28" t="n"/>
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <f>IFERROR(AVERAGE(C22:G22),"")</f>
         <v/>
       </c>
@@ -3349,29 +3949,19 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="D23" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
       <c r="F23" s="28" t="n"/>
-      <c r="G23" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" s="23">
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="22">
         <f>IFERROR(AVERAGE(C23:G23),"")</f>
         <v/>
       </c>
-      <c r="I23" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -3381,7 +3971,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -3389,7 +3979,7 @@
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
-      <c r="H24" s="23">
+      <c r="H24" s="22">
         <f>IFERROR(AVERAGE(C24:G24),"")</f>
         <v/>
       </c>
@@ -3403,19 +3993,15 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
-      <c r="E25" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="F25" s="25" t="n">
-        <v>49</v>
-      </c>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
-      <c r="H25" s="23">
+      <c r="H25" s="22">
         <f>IFERROR(AVERAGE(C25:G25),"")</f>
         <v/>
       </c>
@@ -3429,17 +4015,15 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="E26" s="28" t="n"/>
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
-      <c r="H26" s="23">
+      <c r="H26" s="22">
         <f>IFERROR(AVERAGE(C26:G26),"")</f>
         <v/>
       </c>
@@ -3453,7 +4037,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -3461,7 +4045,7 @@
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
-      <c r="H27" s="23">
+      <c r="H27" s="22">
         <f>IFERROR(AVERAGE(C27:G27),"")</f>
         <v/>
       </c>
@@ -3475,19 +4059,29 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="23">
+      <c r="G28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="22">
         <f>IFERROR(AVERAGE(C28:G28),"")</f>
         <v/>
       </c>
-      <c r="I28" s="28" t="n"/>
+      <c r="I28" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -3497,7 +4091,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -3505,7 +4099,7 @@
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
-      <c r="H29" s="23">
+      <c r="H29" s="22">
         <f>IFERROR(AVERAGE(C29:G29),"")</f>
         <v/>
       </c>
@@ -3519,7 +4113,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -3527,7 +4121,7 @@
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="23">
+      <c r="H30" s="22">
         <f>IFERROR(AVERAGE(C30:G30),"")</f>
         <v/>
       </c>
@@ -3541,25 +4135,23 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="23">
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="22">
         <f>IFERROR(AVERAGE(C31:G31),"")</f>
         <v/>
       </c>
-      <c r="I31" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -3569,31 +4161,19 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="D32" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="F32" s="25" t="n">
-        <v>49</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H32" s="23">
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="22">
         <f>IFERROR(AVERAGE(C32:G32),"")</f>
         <v/>
       </c>
-      <c r="I32" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -3603,15 +4183,17 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="E33" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="23">
+      <c r="H33" s="22">
         <f>IFERROR(AVERAGE(C33:G33),"")</f>
         <v/>
       </c>
@@ -3625,7 +4207,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -3633,7 +4215,7 @@
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="23">
+      <c r="H34" s="22">
         <f>IFERROR(AVERAGE(C34:G34),"")</f>
         <v/>
       </c>
@@ -3647,7 +4229,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -3655,7 +4237,7 @@
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
-      <c r="H35" s="23">
+      <c r="H35" s="22">
         <f>IFERROR(AVERAGE(C35:G35),"")</f>
         <v/>
       </c>
@@ -3669,7 +4251,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -3677,7 +4259,7 @@
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
-      <c r="H36" s="23">
+      <c r="H36" s="22">
         <f>IFERROR(AVERAGE(C36:G36),"")</f>
         <v/>
       </c>
@@ -3691,17 +4273,15 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C37" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
-      <c r="H37" s="23">
+      <c r="H37" s="22">
         <f>IFERROR(AVERAGE(C37:G37),"")</f>
         <v/>
       </c>
@@ -3715,22 +4295,316 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
+      <c r="D38" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="23">
+      <c r="G38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="22">
         <f>IFERROR(AVERAGE(C38:G38),"")</f>
         <v/>
       </c>
-      <c r="I38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="I38" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="22">
+        <f>IFERROR(AVERAGE(C39:G39),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="22">
+        <f>IFERROR(AVERAGE(C40:G40),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="22">
+        <f>IFERROR(AVERAGE(C41:G41),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="22">
+        <f>IFERROR(AVERAGE(C42:G42),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="22">
+        <f>IFERROR(AVERAGE(C43:G43),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="22">
+        <f>IFERROR(AVERAGE(C44:G44),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="22">
+        <f>IFERROR(AVERAGE(C45:G45),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="22">
+        <f>IFERROR(AVERAGE(C46:G46),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="22">
+        <f>IFERROR(AVERAGE(C47:G47),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="22">
+        <f>IFERROR(AVERAGE(C48:G48),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="22">
+        <f>IFERROR(AVERAGE(C49:G49),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="22">
+        <f>IFERROR(AVERAGE(C50:G50),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -3740,7 +4614,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A51:I51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3754,7 +4628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4039,20 +4913,16 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="D12" s="21" t="n"/>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
       <c r="H12" s="21" t="n"/>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
@@ -4066,7 +4936,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
+          <t>Vicki Lucey</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
@@ -4074,18 +4944,16 @@
         <v>87</v>
       </c>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F13" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G13" s="21" t="n"/>
       <c r="H13" s="21" t="n"/>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
-      <c r="J13" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -4095,22 +4963,20 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="D14" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="I14" s="23">
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22">
         <f>IFERROR(AVERAGE(C14:H14),"")</f>
         <v/>
       </c>
@@ -4119,27 +4985,35 @@
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -4149,7 +5023,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -4158,7 +5032,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -4172,7 +5046,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
@@ -4181,7 +5055,7 @@
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
@@ -4195,26 +5069,20 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
-        </is>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
-      <c r="G18" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G18" s="28" t="n"/>
       <c r="H18" s="28" t="n"/>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
-      <c r="J18" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -4224,18 +5092,20 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="n"/>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="23" t="n">
         <v>100</v>
       </c>
       <c r="H19" s="28" t="n"/>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
@@ -4251,22 +5121,24 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="I20" s="23">
+      <c r="G20" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
-      <c r="J20" s="28" t="n"/>
+      <c r="J20" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -4276,7 +5148,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -4285,7 +5157,7 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
@@ -4299,7 +5171,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -4308,7 +5180,7 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
@@ -4322,20 +5194,16 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>DJuan Johnson</t>
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
-      <c r="D23" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
       <c r="H23" s="28" t="n"/>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
@@ -4349,7 +5217,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -4357,8 +5225,10 @@
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="H24" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
@@ -4372,18 +5242,16 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
@@ -4397,22 +5265,16 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
-        </is>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>97</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>95</v>
-      </c>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
       <c r="H26" s="28" t="n"/>
-      <c r="I26" s="23">
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
@@ -4426,7 +5288,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -4435,7 +5297,7 @@
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
@@ -4449,16 +5311,20 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
+      <c r="D28" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
+      <c r="F28" s="25" t="n">
+        <v>47</v>
+      </c>
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
@@ -4472,7 +5338,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -4481,7 +5347,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -4495,7 +5361,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -4504,7 +5370,7 @@
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
@@ -4518,22 +5384,18 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="30" t="n">
-        <v>87</v>
-      </c>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="I31" s="23">
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
@@ -4547,26 +5409,20 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -4576,16 +5432,22 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
@@ -4599,7 +5461,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -4608,7 +5470,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -4622,30 +5484,20 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Kaisha Brewer</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F35" s="25" t="n">
-        <v>47</v>
-      </c>
-      <c r="G35" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
-      <c r="J35" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -4655,7 +5507,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -4664,7 +5516,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -4678,18 +5530,16 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
@@ -4703,23 +5553,325 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="I38" s="22">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="28" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
           <t>Zack Whitten</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
-        <f>IFERROR(AVERAGE(C38:H38),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -4727,9 +5879,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4743,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5028,27 +6180,29 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="n">
+          <t>Robert Cline</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="D12" s="21" t="n"/>
+      <c r="D12" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E12" s="29" t="n">
         <v>95</v>
       </c>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="23">
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="24" t="n">
-        <v>46</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -5059,20 +6213,28 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n"/>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="E13" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
+      <c r="G13" s="25" t="n">
+        <v>60</v>
+      </c>
       <c r="H13" s="21" t="n"/>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
-      <c r="J13" s="21" t="n"/>
+      <c r="J13" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -5082,47 +6244,47 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
-      <c r="E14" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="29" t="n">
         <v>92</v>
       </c>
-      <c r="I14" s="23">
-        <f>IFERROR(AVERAGE(C14:H14),"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -5132,7 +6294,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -5141,7 +6303,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -5155,7 +6317,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
@@ -5164,7 +6326,7 @@
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
@@ -5178,7 +6340,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
@@ -5186,10 +6348,8 @@
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
-      <c r="H18" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I18" s="23">
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
@@ -5203,24 +6363,22 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="23">
+      <c r="H19" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
-      <c r="J19" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -5230,18 +6388,18 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>100</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
@@ -5257,7 +6415,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -5266,7 +6424,7 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
@@ -5280,7 +6438,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -5289,7 +6447,7 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
@@ -5303,32 +6461,20 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="25" t="n">
-        <v>75</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I23" s="23">
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5338,20 +6484,24 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
+      <c r="D24" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E24" s="28" t="n"/>
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
-      <c r="J24" s="28" t="n"/>
+      <c r="J24" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -5361,20 +6511,16 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="25" t="n">
-        <v>75</v>
-      </c>
+      <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
-      <c r="H25" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I25" s="23">
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
@@ -5388,22 +6534,16 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F26" s="25" t="n">
-        <v>75</v>
-      </c>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
-      <c r="H26" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I26" s="23">
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
@@ -5417,7 +6557,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -5426,7 +6566,7 @@
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
@@ -5440,20 +6580,32 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="F28" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
-      <c r="J28" s="28" t="n"/>
+      <c r="J28" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -5463,7 +6615,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -5472,7 +6624,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -5486,7 +6638,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -5495,7 +6647,7 @@
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
@@ -5509,28 +6661,24 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
-      <c r="E31" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H31" s="28" t="n"/>
-      <c r="I31" s="23">
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -5540,28 +6688,20 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I32" s="23">
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -5571,16 +6711,22 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="28" t="n"/>
+      <c r="E33" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F33" s="25" t="n">
+        <v>75</v>
+      </c>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="n"/>
-      <c r="I33" s="23">
+      <c r="H33" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
@@ -5594,7 +6740,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -5603,7 +6749,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -5617,18 +6763,16 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
@@ -5642,7 +6786,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -5651,7 +6795,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -5665,7 +6809,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -5674,7 +6818,7 @@
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
@@ -5688,23 +6832,329 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="22">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>84.33</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
           <t>Zack Whitten</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
-        <f>IFERROR(AVERAGE(C38:H38),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -5712,9 +7162,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5728,7 +7178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6013,27 +7463,23 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="D12" s="22" t="n">
+          <t>Robert Cline</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="24" t="n">
-        <v>122.67</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -6044,20 +7490,28 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
+      <c r="F13" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G13" s="21" t="n"/>
       <c r="H13" s="21" t="n"/>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
-      <c r="J13" s="21" t="n"/>
+      <c r="J13" s="24" t="n">
+        <v>122.67</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6067,7 +7521,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
@@ -6076,34 +7530,34 @@
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
       <c r="H14" s="21" t="n"/>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f>IFERROR(AVERAGE(C14:H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -6113,7 +7567,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -6122,7 +7576,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -6136,20 +7590,24 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
       <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
+      <c r="G17" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
-      <c r="J17" s="28" t="n"/>
+      <c r="J17" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -6159,7 +7617,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
@@ -6168,7 +7626,7 @@
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="28" t="n"/>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
@@ -6182,24 +7640,20 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
       <c r="H19" s="28" t="n"/>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
-      <c r="J19" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -6209,20 +7663,24 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
+      <c r="D20" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
-      <c r="J20" s="28" t="n"/>
+      <c r="J20" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -6232,7 +7690,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -6241,7 +7699,7 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
@@ -6255,7 +7713,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -6264,7 +7722,7 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
@@ -6278,28 +7736,20 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="29" t="n">
-        <v>95</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E23" s="28" t="n"/>
       <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
-      <c r="H23" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="23">
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -6309,7 +7759,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -6318,7 +7768,7 @@
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
@@ -6332,7 +7782,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
@@ -6341,7 +7791,7 @@
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
@@ -6355,26 +7805,20 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E26" s="28" t="n"/>
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
-      <c r="H26" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="23">
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
-      <c r="J26" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -6384,20 +7828,24 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n"/>
+      <c r="G27" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
-      <c r="J27" s="28" t="n"/>
+      <c r="J27" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -6407,23 +7855,27 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="H28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="24" t="n">
-        <v>46</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -6434,7 +7886,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -6443,7 +7895,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -6457,7 +7909,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -6466,7 +7918,7 @@
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
@@ -6480,26 +7932,20 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>100</v>
-      </c>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
       <c r="H31" s="28" t="n"/>
-      <c r="I31" s="23">
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -6509,30 +7955,20 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H32" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I32" s="23">
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="24" t="n">
-        <v>230</v>
-      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -6542,20 +7978,26 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="E33" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="n"/>
-      <c r="I33" s="23">
+      <c r="H33" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="J33" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -6565,7 +8007,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -6574,7 +8016,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -6588,25 +8030,23 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="D35" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
-      <c r="H35" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="23">
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="24" t="n">
-        <v>38.33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
@@ -6617,7 +8057,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -6626,7 +8066,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -6640,7 +8080,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -6649,7 +8089,7 @@
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
@@ -6663,18 +8103,20 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="22" t="n">
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="D38" s="23" t="n">
         <v>100</v>
       </c>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
+      <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
@@ -6682,8 +8124,310 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>191.67</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>76.67</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -6691,9 +8435,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +8451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6992,24 +8736,30 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
         <v>85</v>
       </c>
       <c r="D12" s="21" t="n"/>
-      <c r="E12" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="23">
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
-      <c r="J12" s="21" t="n"/>
+      <c r="J12" s="24" t="n">
+        <v>147.86</v>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -7019,16 +8769,18 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n"/>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
       <c r="H13" s="21" t="n"/>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
@@ -7042,7 +8794,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
@@ -7051,34 +8803,34 @@
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
       <c r="H14" s="21" t="n"/>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f>IFERROR(AVERAGE(C14:H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -7088,7 +8840,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -7097,7 +8849,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -7111,7 +8863,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
@@ -7120,7 +8872,7 @@
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
@@ -7134,7 +8886,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
@@ -7143,7 +8895,7 @@
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="28" t="n"/>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
@@ -7157,7 +8909,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
@@ -7166,7 +8918,7 @@
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
       <c r="H19" s="28" t="n"/>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
@@ -7180,7 +8932,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -7189,7 +8941,7 @@
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
@@ -7203,20 +8955,26 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
+      <c r="F21" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="G21" s="28" t="n"/>
-      <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="H21" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
-      <c r="J21" s="28" t="n"/>
+      <c r="J21" s="24" t="n">
+        <v>32.86</v>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -7226,7 +8984,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
@@ -7235,7 +8993,7 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
@@ -7249,30 +9007,22 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>85</v>
-      </c>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="F23" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G23" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
       <c r="H23" s="28" t="n"/>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -7282,7 +9032,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -7291,7 +9041,7 @@
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
@@ -7305,7 +9055,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
@@ -7314,7 +9064,7 @@
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
@@ -7328,30 +9078,20 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
-        </is>
-      </c>
-      <c r="C26" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>0</v>
-      </c>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
       <c r="H26" s="28" t="n"/>
-      <c r="I26" s="23">
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
-      <c r="J26" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -7361,16 +9101,18 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="E27" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
@@ -7384,16 +9126,18 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
@@ -7407,7 +9151,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -7416,7 +9160,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -7430,7 +9174,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -7438,12 +9182,16 @@
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="H30" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="28" t="n"/>
+      <c r="J30" s="24" t="n">
+        <v>32.86</v>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7453,26 +9201,20 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>85</v>
-      </c>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="23">
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>76.67</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -7482,18 +9224,16 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>85</v>
-      </c>
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
@@ -7507,16 +9247,18 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
+      <c r="D33" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
@@ -7530,7 +9272,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -7539,7 +9281,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -7553,26 +9295,20 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
-      <c r="G35" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
-      <c r="J35" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -7582,7 +9318,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -7591,7 +9327,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -7605,7 +9341,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -7614,7 +9350,7 @@
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
@@ -7628,7 +9364,7 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
@@ -7636,15 +9372,315 @@
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
+      <c r="H38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
-      <c r="J38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="J38" s="24" t="n">
+        <v>32.86</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>147.86</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="24" t="n">
+        <v>32.86</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>32.86</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -7652,9 +9688,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7668,7 +9704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7953,20 +9989,18 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>100</v>
       </c>
       <c r="G12" s="21" t="n"/>
-      <c r="H12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="23">
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="22">
         <f>IFERROR(AVERAGE(C12:H12),"")</f>
         <v/>
       </c>
@@ -7982,7 +10016,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
+          <t>Vicki Lucey</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
@@ -7990,8 +10024,10 @@
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="23">
+      <c r="H13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="22">
         <f>IFERROR(AVERAGE(C13:H13),"")</f>
         <v/>
       </c>
@@ -8005,7 +10041,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
@@ -8014,34 +10050,34 @@
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
       <c r="H14" s="21" t="n"/>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f>IFERROR(AVERAGE(C14:H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="23">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22">
         <f>IFERROR(AVERAGE(C15:H15),"")</f>
         <v/>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -8051,7 +10087,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -8060,7 +10096,7 @@
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f>IFERROR(AVERAGE(C16:H16),"")</f>
         <v/>
       </c>
@@ -8074,20 +10110,26 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="n"/>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="E17" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
       <c r="H17" s="28" t="n"/>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>IFERROR(AVERAGE(C17:H17),"")</f>
         <v/>
       </c>
-      <c r="J17" s="28" t="n"/>
+      <c r="J17" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -8097,7 +10139,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
@@ -8106,7 +10148,7 @@
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="28" t="n"/>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <f>IFERROR(AVERAGE(C18:H18),"")</f>
         <v/>
       </c>
@@ -8120,7 +10162,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
@@ -8128,10 +10170,8 @@
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
-      <c r="H19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="23">
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="22">
         <f>IFERROR(AVERAGE(C19:H19),"")</f>
         <v/>
       </c>
@@ -8145,7 +10185,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -8154,7 +10194,7 @@
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="28" t="n"/>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <f>IFERROR(AVERAGE(C20:H20),"")</f>
         <v/>
       </c>
@@ -8168,7 +10208,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
@@ -8177,7 +10217,7 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <f>IFERROR(AVERAGE(C21:H21),"")</f>
         <v/>
       </c>
@@ -8191,20 +10231,24 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
+      <c r="F22" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="28" t="n"/>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <f>IFERROR(AVERAGE(C22:H22),"")</f>
         <v/>
       </c>
-      <c r="J22" s="28" t="n"/>
+      <c r="J22" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -8214,24 +10258,20 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>DJuan Johnson</t>
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
       <c r="H23" s="28" t="n"/>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <f>IFERROR(AVERAGE(C23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -8241,7 +10281,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -8250,7 +10290,7 @@
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="28" t="n"/>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <f>IFERROR(AVERAGE(C24:H24),"")</f>
         <v/>
       </c>
@@ -8264,7 +10304,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
@@ -8273,7 +10313,7 @@
       <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
       <c r="H25" s="28" t="n"/>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <f>IFERROR(AVERAGE(C25:H25),"")</f>
         <v/>
       </c>
@@ -8287,7 +10327,7 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
@@ -8296,7 +10336,7 @@
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
       <c r="H26" s="28" t="n"/>
-      <c r="I26" s="23">
+      <c r="I26" s="22">
         <f>IFERROR(AVERAGE(C26:H26),"")</f>
         <v/>
       </c>
@@ -8310,7 +10350,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -8318,8 +10358,10 @@
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
-      <c r="H27" s="28" t="n"/>
-      <c r="I27" s="23">
+      <c r="H27" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
@@ -8333,7 +10375,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -8342,7 +10384,7 @@
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
@@ -8356,7 +10398,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -8365,7 +10407,7 @@
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
@@ -8379,20 +10421,26 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
+      <c r="D30" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
+      <c r="F30" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="28" t="n"/>
+      <c r="J30" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -8402,26 +10450,20 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
       <c r="H31" s="28" t="n"/>
-      <c r="I31" s="23">
+      <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -8431,7 +10473,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -8440,7 +10482,7 @@
       <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="n"/>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
@@ -8454,7 +10496,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -8463,7 +10505,7 @@
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
@@ -8477,7 +10519,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -8486,7 +10528,7 @@
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
@@ -8500,7 +10542,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -8509,7 +10551,7 @@
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
       <c r="H35" s="28" t="n"/>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
@@ -8523,7 +10565,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -8532,7 +10574,7 @@
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
       <c r="H36" s="28" t="n"/>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
@@ -8546,7 +10588,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -8555,7 +10597,7 @@
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
       <c r="H37" s="28" t="n"/>
-      <c r="I37" s="23">
+      <c r="I37" s="22">
         <f>IFERROR(AVERAGE(C37:H37),"")</f>
         <v/>
       </c>
@@ -8569,23 +10611,315 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
+      <c r="D38" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
-      <c r="I38" s="23">
+      <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="28" t="n"/>
     </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="28" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="24" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -8593,9 +10927,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8609,15 +10943,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8642,10 +10977,15 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -8668,8 +11008,13 @@
           <t>09/22</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>09/23</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -8688,8 +11033,13 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -8704,8 +11054,11 @@
       <c r="D5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="E5" s="12" t="n">
+        <v>34</v>
+      </c>
       <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -8718,6 +11071,7 @@
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -8730,6 +11084,7 @@
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -8742,6 +11097,7 @@
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -8754,6 +11110,7 @@
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -8766,6 +11123,7 @@
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -8775,12 +11133,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -8794,16 +11153,21 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Vicki Lucey</t>
+          <t>Robert Cline</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="23">
-        <f>IFERROR(AVERAGE(C12:D12),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="21" t="n"/>
+      <c r="D12" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="22">
+        <f>IFERROR(AVERAGE(C12:E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -8813,16 +11177,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Kasey Wilson</t>
+          <t>Vicki Lucey</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="23">
-        <f>IFERROR(AVERAGE(C13:D13),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="22">
+        <f>IFERROR(AVERAGE(C13:E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -8832,35 +11197,37 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Nathan Roberts</t>
+          <t>Kasey Wilson</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
-      <c r="E14" s="23">
-        <f>IFERROR(AVERAGE(C14:D14),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="22">
+        <f>IFERROR(AVERAGE(C14:E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>CREW</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Ailen Gonzalez Cardero</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="23">
-        <f>IFERROR(AVERAGE(C15:D15),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="n"/>
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="22">
+        <f>IFERROR(AVERAGE(C15:E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -8870,16 +11237,19 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Anthony Pirtle</t>
+          <t>Ailen Gonzalez Cardero</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
-      <c r="E16" s="23">
-        <f>IFERROR(AVERAGE(C16:D16),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="28" t="n"/>
+      <c r="E16" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" s="22">
+        <f>IFERROR(AVERAGE(C16:E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -8889,16 +11259,17 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Anthony Pirtle</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="23">
-        <f>IFERROR(AVERAGE(C17:D17),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="22">
+        <f>IFERROR(AVERAGE(C17:E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -8908,16 +11279,17 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Autumn Hearn</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
-      <c r="E18" s="23">
-        <f>IFERROR(AVERAGE(C18:D18),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="22">
+        <f>IFERROR(AVERAGE(C18:E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -8927,16 +11299,17 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Brianna Gatewood</t>
+          <t>Autumn Hearn</t>
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
-      <c r="E19" s="23">
-        <f>IFERROR(AVERAGE(C19:D19),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="22">
+        <f>IFERROR(AVERAGE(C19:E19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -8946,16 +11319,17 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>DaKayla Dorsey</t>
+          <t>Brianna Gatewood</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="23">
-        <f>IFERROR(AVERAGE(C20:D20),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="22">
+        <f>IFERROR(AVERAGE(C20:E20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -8965,16 +11339,17 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Christopher Conder</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
-      <c r="E21" s="23">
-        <f>IFERROR(AVERAGE(C21:D21),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="22">
+        <f>IFERROR(AVERAGE(C21:E21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -8984,16 +11359,21 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Divan</t>
+          <t>Cortez Brown</t>
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="23">
-        <f>IFERROR(AVERAGE(C22:D22),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="28" t="n"/>
+      <c r="D22" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="22">
+        <f>IFERROR(AVERAGE(C22:E22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -9003,16 +11383,17 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>DJuan Johnson</t>
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="23">
-        <f>IFERROR(AVERAGE(C23:D23),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="22">
+        <f>IFERROR(AVERAGE(C23:E23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -9022,16 +11403,17 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>DaKayla Dorsey</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
-      <c r="E24" s="23">
-        <f>IFERROR(AVERAGE(C24:D24),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="22">
+        <f>IFERROR(AVERAGE(C24:E24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -9041,16 +11423,17 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
-      <c r="E25" s="23">
-        <f>IFERROR(AVERAGE(C25:D25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="22">
+        <f>IFERROR(AVERAGE(C25:E25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -9060,16 +11443,17 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Divan</t>
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="23">
-        <f>IFERROR(AVERAGE(C26:D26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="22">
+        <f>IFERROR(AVERAGE(C26:E26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -9079,16 +11463,17 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="23">
-        <f>IFERROR(AVERAGE(C27:D27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="22">
+        <f>IFERROR(AVERAGE(C27:E27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -9098,16 +11483,19 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="23">
-        <f>IFERROR(AVERAGE(C28:D28),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="28" t="n"/>
+      <c r="E28" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="F28" s="22">
+        <f>IFERROR(AVERAGE(C28:E28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -9117,16 +11505,17 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="23">
-        <f>IFERROR(AVERAGE(C29:D29),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="22">
+        <f>IFERROR(AVERAGE(C29:E29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -9136,16 +11525,17 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
-      <c r="E30" s="23">
-        <f>IFERROR(AVERAGE(C30:D30),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="22">
+        <f>IFERROR(AVERAGE(C30:E30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -9155,20 +11545,17 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E31" s="23">
-        <f>IFERROR(AVERAGE(C31:D31),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="24" t="n">
-        <v>115</v>
-      </c>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="22">
+        <f>IFERROR(AVERAGE(C31:E31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -9178,16 +11565,17 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="23">
-        <f>IFERROR(AVERAGE(C32:D32),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="22">
+        <f>IFERROR(AVERAGE(C32:E32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -9197,16 +11585,17 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="23">
-        <f>IFERROR(AVERAGE(C33:D33),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="22">
+        <f>IFERROR(AVERAGE(C33:E33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -9216,16 +11605,17 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="23">
-        <f>IFERROR(AVERAGE(C34:D34),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="22">
+        <f>IFERROR(AVERAGE(C34:E34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -9235,16 +11625,17 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
-      <c r="E35" s="23">
-        <f>IFERROR(AVERAGE(C35:D35),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="22">
+        <f>IFERROR(AVERAGE(C35:E35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -9254,16 +11645,17 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
-      <c r="E36" s="23">
-        <f>IFERROR(AVERAGE(C36:D36),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="22">
+        <f>IFERROR(AVERAGE(C36:E36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -9273,16 +11665,17 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
-      <c r="E37" s="23">
-        <f>IFERROR(AVERAGE(C37:D37),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="22">
+        <f>IFERROR(AVERAGE(C37:E37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -9292,19 +11685,272 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="22">
+        <f>IFERROR(AVERAGE(C38:E38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="22">
+        <f>IFERROR(AVERAGE(C39:E39),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="22">
+        <f>IFERROR(AVERAGE(C40:E40),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="22">
+        <f>IFERROR(AVERAGE(C41:E41),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="22">
+        <f>IFERROR(AVERAGE(C42:E42),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="22">
+        <f>IFERROR(AVERAGE(C43:E43),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="22">
+        <f>IFERROR(AVERAGE(C44:E44),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="22">
+        <f>IFERROR(AVERAGE(C45:E45),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="22">
+        <f>IFERROR(AVERAGE(C46:E46),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="22">
+        <f>IFERROR(AVERAGE(C47:E47),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="22">
+        <f>IFERROR(AVERAGE(C48:E48),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="22">
+        <f>IFERROR(AVERAGE(C49:E49),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
           <t>Zack Whitten</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="23">
-        <f>IFERROR(AVERAGE(C38:D38),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="22">
+        <f>IFERROR(AVERAGE(C50:E50),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="24" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -9312,9 +11958,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -1478,34 +1478,22 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="D28" s="25" t="n">
-        <v>0</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G28" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
       <c r="I28" s="28" t="n"/>
-      <c r="J28" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J28" s="28" t="n"/>
       <c r="K28" s="22">
         <f>IFERROR(AVERAGE(C28:J28),"")</f>
         <v/>
       </c>
-      <c r="L28" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -1515,22 +1503,34 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
+      <c r="F29" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H29" s="28" t="n"/>
       <c r="I29" s="28" t="n"/>
-      <c r="J29" s="28" t="n"/>
+      <c r="J29" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K29" s="22">
         <f>IFERROR(AVERAGE(C29:J29),"")</f>
         <v/>
       </c>
-      <c r="L29" s="28" t="n"/>
+      <c r="L29" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -1565,13 +1565,11 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
@@ -1592,11 +1590,13 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
+      <c r="D32" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
@@ -1617,32 +1617,22 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
       <c r="I33" s="28" t="n"/>
-      <c r="J33" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J33" s="28" t="n"/>
       <c r="K33" s="22">
         <f>IFERROR(AVERAGE(C33:J33),"")</f>
         <v/>
       </c>
-      <c r="L33" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -1652,22 +1642,32 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
+      <c r="E34" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H34" s="28" t="n"/>
       <c r="I34" s="28" t="n"/>
-      <c r="J34" s="28" t="n"/>
+      <c r="J34" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K34" s="22">
         <f>IFERROR(AVERAGE(C34:J34),"")</f>
         <v/>
       </c>
-      <c r="L34" s="28" t="n"/>
+      <c r="L34" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -1752,30 +1752,22 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
-      <c r="E38" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
       <c r="I38" s="28" t="n"/>
-      <c r="J38" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J38" s="28" t="n"/>
       <c r="K38" s="22">
         <f>IFERROR(AVERAGE(C38:J38),"")</f>
         <v/>
       </c>
-      <c r="L38" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="L38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -1785,22 +1777,30 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="28" t="n"/>
-      <c r="E39" s="28" t="n"/>
+      <c r="E39" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n"/>
+      <c r="G39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H39" s="28" t="n"/>
       <c r="I39" s="28" t="n"/>
-      <c r="J39" s="28" t="n"/>
+      <c r="J39" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K39" s="22">
         <f>IFERROR(AVERAGE(C39:J39),"")</f>
         <v/>
       </c>
-      <c r="L39" s="28" t="n"/>
+      <c r="L39" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -1810,36 +1810,22 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
+          <t>Madelynn Smith</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
-      <c r="D40" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
-      <c r="F40" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="J40" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="28" t="n"/>
+      <c r="J40" s="28" t="n"/>
       <c r="K40" s="22">
         <f>IFERROR(AVERAGE(C40:J40),"")</f>
         <v/>
       </c>
-      <c r="L40" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="L40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -1849,7 +1835,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
@@ -1863,17 +1849,21 @@
       <c r="G41" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="H41" s="28" t="n"/>
+      <c r="H41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I41" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="J41" s="28" t="n"/>
+      <c r="J41" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K41" s="22">
         <f>IFERROR(AVERAGE(C41:J41),"")</f>
         <v/>
       </c>
       <c r="L41" s="24" t="n">
-        <v>38.33</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
@@ -1884,32 +1874,32 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C42" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="30" t="n">
-        <v>80</v>
-      </c>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="28" t="n"/>
       <c r="F42" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="G42" s="28" t="n"/>
+      <c r="G42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H42" s="28" t="n"/>
       <c r="I42" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="J42" s="30" t="n">
-        <v>85</v>
-      </c>
+      <c r="J42" s="28" t="n"/>
       <c r="K42" s="22">
         <f>IFERROR(AVERAGE(C42:J42),"")</f>
         <v/>
       </c>
-      <c r="L42" s="28" t="n"/>
+      <c r="L42" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -1919,17 +1909,27 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="n"/>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="D43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
-      <c r="F43" s="28" t="n"/>
+      <c r="E43" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="G43" s="28" t="n"/>
       <c r="H43" s="28" t="n"/>
-      <c r="I43" s="28" t="n"/>
-      <c r="J43" s="28" t="n"/>
+      <c r="I43" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J43" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="K43" s="22">
         <f>IFERROR(AVERAGE(C43:J43),"")</f>
         <v/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -2044,32 +2044,22 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
-      <c r="D48" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
-      <c r="F48" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="F48" s="28" t="n"/>
       <c r="G48" s="28" t="n"/>
-      <c r="H48" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="I48" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="28" t="n"/>
       <c r="J48" s="28" t="n"/>
       <c r="K48" s="22">
         <f>IFERROR(AVERAGE(C48:J48),"")</f>
         <v/>
       </c>
-      <c r="L48" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="L48" s="28" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -2079,22 +2069,32 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
-      <c r="D49" s="28" t="n"/>
+      <c r="D49" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="28" t="n"/>
-      <c r="F49" s="28" t="n"/>
+      <c r="F49" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="G49" s="28" t="n"/>
-      <c r="H49" s="28" t="n"/>
-      <c r="I49" s="28" t="n"/>
+      <c r="H49" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I49" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="J49" s="28" t="n"/>
       <c r="K49" s="22">
         <f>IFERROR(AVERAGE(C49:J49),"")</f>
         <v/>
       </c>
-      <c r="L49" s="28" t="n"/>
+      <c r="L49" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
@@ -2121,8 +2121,33 @@
       </c>
       <c r="L50" s="28" t="n"/>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="28" t="n"/>
+      <c r="J51" s="28" t="n"/>
+      <c r="K51" s="22">
+        <f>IFERROR(AVERAGE(C51:J51),"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -2130,9 +2155,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A52:L52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2146,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2790,7 +2815,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -2813,28 +2838,20 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
       <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
-      <c r="J28" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -2844,20 +2861,28 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="E29" s="25" t="n">
+        <v>69</v>
+      </c>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
+      <c r="G29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H29" s="28" t="n"/>
       <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
-      <c r="J29" s="28" t="n"/>
+      <c r="J29" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -2867,7 +2892,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -2890,26 +2915,20 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="H31" s="28" t="n"/>
       <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -2919,20 +2938,26 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
+      <c r="F32" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
+      <c r="H32" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
       </c>
-      <c r="J32" s="28" t="n"/>
+      <c r="J32" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -2942,30 +2967,20 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
       <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
-      <c r="J33" s="24" t="n">
-        <v>122.67</v>
-      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -2975,20 +2990,30 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
-        </is>
-      </c>
-      <c r="C34" s="28" t="n"/>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
+      <c r="F34" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
-      <c r="J34" s="28" t="n"/>
+      <c r="J34" s="24" t="n">
+        <v>122.67</v>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -2998,7 +3023,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -3021,7 +3046,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -3044,7 +3069,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -3067,28 +3092,20 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
-      <c r="E38" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
       <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
-      <c r="J38" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -3098,20 +3115,28 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="n"/>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D39" s="28" t="n"/>
-      <c r="E39" s="28" t="n"/>
+      <c r="E39" s="25" t="n">
+        <v>69</v>
+      </c>
       <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n"/>
+      <c r="G39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H39" s="28" t="n"/>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="J39" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -3121,30 +3146,20 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
-      <c r="F40" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F40" s="28" t="n"/>
       <c r="G40" s="28" t="n"/>
-      <c r="H40" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="H40" s="28" t="n"/>
       <c r="I40" s="22">
         <f>IFERROR(AVERAGE(C40:H40),"")</f>
         <v/>
       </c>
-      <c r="J40" s="24" t="n">
-        <v>161</v>
-      </c>
+      <c r="J40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -3154,29 +3169,29 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C41" s="28" t="n"/>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D41" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="E41" s="25" t="n">
-        <v>69</v>
-      </c>
+      <c r="E41" s="28" t="n"/>
       <c r="F41" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="G41" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(C41:H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="24" t="n">
-        <v>153.33</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
@@ -3187,29 +3202,29 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n">
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="D42" s="28" t="n"/>
       <c r="E42" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="F42" s="28" t="n"/>
+      <c r="F42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G42" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="H42" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="H42" s="28" t="n"/>
       <c r="I42" s="22">
         <f>IFERROR(AVERAGE(C42:H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="24" t="n">
-        <v>84.33</v>
+        <v>153.33</v>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
@@ -3220,20 +3235,30 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="n"/>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
+      <c r="E43" s="25" t="n">
+        <v>69</v>
+      </c>
       <c r="F43" s="28" t="n"/>
-      <c r="G43" s="28" t="n"/>
-      <c r="H43" s="28" t="n"/>
+      <c r="G43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="I43" s="22">
         <f>IFERROR(AVERAGE(C43:H43),"")</f>
         <v/>
       </c>
-      <c r="J43" s="28" t="n"/>
+      <c r="J43" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
@@ -3243,7 +3268,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -3266,7 +3291,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -3289,7 +3314,7 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
@@ -3312,7 +3337,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -3335,26 +3360,20 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
-      <c r="D48" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
-      <c r="F48" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F48" s="28" t="n"/>
       <c r="G48" s="28" t="n"/>
       <c r="H48" s="28" t="n"/>
       <c r="I48" s="22">
         <f>IFERROR(AVERAGE(C48:H48),"")</f>
         <v/>
       </c>
-      <c r="J48" s="24" t="n">
-        <v>115</v>
-      </c>
+      <c r="J48" s="28" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -3364,20 +3383,26 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
-      <c r="D49" s="28" t="n"/>
+      <c r="D49" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E49" s="28" t="n"/>
-      <c r="F49" s="28" t="n"/>
+      <c r="F49" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G49" s="28" t="n"/>
       <c r="H49" s="28" t="n"/>
       <c r="I49" s="22">
         <f>IFERROR(AVERAGE(C49:H49),"")</f>
         <v/>
       </c>
-      <c r="J49" s="28" t="n"/>
+      <c r="J49" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -3387,7 +3412,7 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
@@ -3402,8 +3427,31 @@
       </c>
       <c r="J50" s="28" t="n"/>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -3411,9 +3459,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3427,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4037,7 +4085,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -4059,29 +4107,19 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="D28" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G28" s="28" t="n"/>
       <c r="H28" s="22">
         <f>IFERROR(AVERAGE(C28:G28),"")</f>
         <v/>
       </c>
-      <c r="I28" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -4091,19 +4129,29 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
+      <c r="G29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H29" s="22">
         <f>IFERROR(AVERAGE(C29:G29),"")</f>
         <v/>
       </c>
-      <c r="I29" s="28" t="n"/>
+      <c r="I29" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -4113,7 +4161,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -4135,17 +4183,13 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
-      <c r="E31" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>49</v>
-      </c>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
       <c r="H31" s="22">
         <f>IFERROR(AVERAGE(C31:G31),"")</f>
@@ -4161,13 +4205,17 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
+      <c r="E32" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>49</v>
+      </c>
       <c r="G32" s="28" t="n"/>
       <c r="H32" s="22">
         <f>IFERROR(AVERAGE(C32:G32),"")</f>
@@ -4183,14 +4231,12 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="22">
@@ -4207,12 +4253,14 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="E34" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="22">
@@ -4229,7 +4277,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -4251,7 +4299,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -4273,7 +4321,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -4295,25 +4343,19 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G38" s="28" t="n"/>
       <c r="H38" s="22">
         <f>IFERROR(AVERAGE(C38:G38),"")</f>
         <v/>
       </c>
-      <c r="I38" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -4323,19 +4365,25 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
+      <c r="D39" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n"/>
+      <c r="G39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H39" s="22">
         <f>IFERROR(AVERAGE(C39:G39),"")</f>
         <v/>
       </c>
-      <c r="I39" s="28" t="n"/>
+      <c r="I39" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -4345,29 +4393,19 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="D40" s="30" t="n">
-        <v>80</v>
-      </c>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
-      <c r="F40" s="25" t="n">
-        <v>49</v>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
       <c r="H40" s="22">
         <f>IFERROR(AVERAGE(C40:G40),"")</f>
         <v/>
       </c>
-      <c r="I40" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="I40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -4377,7 +4415,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="25" t="n">
@@ -4386,9 +4424,7 @@
       <c r="D41" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="E41" s="25" t="n">
-        <v>72</v>
-      </c>
+      <c r="E41" s="28" t="n"/>
       <c r="F41" s="25" t="n">
         <v>49</v>
       </c>
@@ -4411,19 +4447,31 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H42" s="22">
         <f>IFERROR(AVERAGE(C42:G42),"")</f>
         <v/>
       </c>
-      <c r="I42" s="28" t="n"/>
+      <c r="I42" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -4433,7 +4481,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -4455,7 +4503,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -4477,7 +4525,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -4499,7 +4547,7 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
@@ -4521,7 +4569,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -4543,12 +4591,10 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="n">
-        <v>72</v>
-      </c>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
       <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
       <c r="F48" s="28" t="n"/>
@@ -4567,10 +4613,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
-        </is>
-      </c>
-      <c r="C49" s="28" t="n"/>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="n">
+        <v>72</v>
+      </c>
       <c r="D49" s="28" t="n"/>
       <c r="E49" s="28" t="n"/>
       <c r="F49" s="28" t="n"/>
@@ -4589,7 +4637,7 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
@@ -4603,8 +4651,30 @@
       </c>
       <c r="I50" s="28" t="n"/>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="22">
+        <f>IFERROR(AVERAGE(C51:G51),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -4614,7 +4684,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A52:I52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4628,7 +4698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5288,7 +5358,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -5311,17 +5381,13 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
       <c r="I28" s="22">
@@ -5338,13 +5404,17 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
+      <c r="D29" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
+      <c r="F29" s="25" t="n">
+        <v>47</v>
+      </c>
       <c r="G29" s="28" t="n"/>
       <c r="H29" s="28" t="n"/>
       <c r="I29" s="22">
@@ -5361,7 +5431,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -5384,12 +5454,10 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Heather Uebelacker-Maddox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
@@ -5409,10 +5477,12 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n"/>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
@@ -5432,18 +5502,12 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="n">
-        <v>97</v>
-      </c>
-      <c r="D33" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>95</v>
-      </c>
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
       <c r="H33" s="28" t="n"/>
@@ -5461,12 +5525,18 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
-        </is>
-      </c>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="D34" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="n"/>
@@ -5484,7 +5554,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -5507,7 +5577,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -5530,7 +5600,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -5553,21 +5623,15 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="25" t="n">
-        <v>47</v>
-      </c>
+      <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="H38" s="28" t="n"/>
       <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
@@ -5582,15 +5646,21 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
+      <c r="D39" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="E39" s="28" t="n"/>
-      <c r="F39" s="28" t="n"/>
+      <c r="F39" s="25" t="n">
+        <v>47</v>
+      </c>
       <c r="G39" s="28" t="n"/>
-      <c r="H39" s="28" t="n"/>
+      <c r="H39" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
@@ -5605,12 +5675,10 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
       <c r="F40" s="28" t="n"/>
@@ -5630,7 +5698,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="29" t="n">
@@ -5639,17 +5707,13 @@
       <c r="D41" s="28" t="n"/>
       <c r="E41" s="28" t="n"/>
       <c r="F41" s="28" t="n"/>
-      <c r="G41" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G41" s="28" t="n"/>
       <c r="H41" s="28" t="n"/>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(C41:H41),"")</f>
         <v/>
       </c>
-      <c r="J41" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J41" s="28" t="n"/>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -5659,20 +5723,26 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="n"/>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D42" s="28" t="n"/>
       <c r="E42" s="28" t="n"/>
       <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
+      <c r="G42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H42" s="28" t="n"/>
       <c r="I42" s="22">
         <f>IFERROR(AVERAGE(C42:H42),"")</f>
         <v/>
       </c>
-      <c r="J42" s="28" t="n"/>
+      <c r="J42" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -5682,7 +5752,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -5705,7 +5775,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -5728,30 +5798,20 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
       <c r="D45" s="28" t="n"/>
-      <c r="E45" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>47</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
       <c r="H45" s="28" t="n"/>
       <c r="I45" s="22">
         <f>IFERROR(AVERAGE(C45:H45),"")</f>
         <v/>
       </c>
-      <c r="J45" s="24" t="n">
-        <v>38.33</v>
-      </c>
+      <c r="J45" s="28" t="n"/>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
@@ -5761,20 +5821,30 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="n"/>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="28" t="n"/>
-      <c r="G46" s="28" t="n"/>
+      <c r="E46" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="H46" s="28" t="n"/>
       <c r="I46" s="22">
         <f>IFERROR(AVERAGE(C46:H46),"")</f>
         <v/>
       </c>
-      <c r="J46" s="28" t="n"/>
+      <c r="J46" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -5784,7 +5854,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -5807,12 +5877,10 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="n">
-        <v>97</v>
-      </c>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
       <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
       <c r="F48" s="28" t="n"/>
@@ -5832,10 +5900,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
-        </is>
-      </c>
-      <c r="C49" s="28" t="n"/>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>97</v>
+      </c>
       <c r="D49" s="28" t="n"/>
       <c r="E49" s="28" t="n"/>
       <c r="F49" s="28" t="n"/>
@@ -5855,7 +5925,7 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
@@ -5870,8 +5940,31 @@
       </c>
       <c r="J50" s="28" t="n"/>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -5879,9 +5972,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5895,7 +5988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6557,7 +6650,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -6580,32 +6673,20 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D28" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="25" t="n">
-        <v>75</v>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>92</v>
-      </c>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
       <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
       </c>
-      <c r="J28" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -6615,20 +6696,32 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
-      <c r="H29" s="28" t="n"/>
+      <c r="F29" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
-      <c r="J29" s="28" t="n"/>
+      <c r="J29" s="24" t="n">
+        <v>84.33</v>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -6638,7 +6731,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -6661,19 +6754,15 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="25" t="n">
-        <v>75</v>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="29" t="n">
-        <v>92</v>
-      </c>
+      <c r="H31" s="28" t="n"/>
       <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
@@ -6688,15 +6777,19 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
+      <c r="F32" s="25" t="n">
+        <v>75</v>
+      </c>
       <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
+      <c r="H32" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="I32" s="22">
         <f>IFERROR(AVERAGE(C32:H32),"")</f>
         <v/>
@@ -6711,21 +6804,15 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>75</v>
-      </c>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="29" t="n">
-        <v>92</v>
-      </c>
+      <c r="H33" s="28" t="n"/>
       <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
@@ -6740,15 +6827,21 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
+      <c r="E34" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>75</v>
+      </c>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
+      <c r="H34" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
@@ -6763,7 +6856,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -6786,7 +6879,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -6809,7 +6902,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -6832,28 +6925,20 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
-      <c r="E38" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="25" t="n">
-        <v>60</v>
-      </c>
+      <c r="G38" s="28" t="n"/>
       <c r="H38" s="28" t="n"/>
       <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
-      <c r="J38" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -6863,20 +6948,28 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="n"/>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D39" s="28" t="n"/>
-      <c r="E39" s="28" t="n"/>
+      <c r="E39" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n"/>
+      <c r="G39" s="25" t="n">
+        <v>60</v>
+      </c>
       <c r="H39" s="28" t="n"/>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="J39" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -6886,32 +6979,20 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>75</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>60</v>
-      </c>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
       <c r="H40" s="28" t="n"/>
       <c r="I40" s="22">
         <f>IFERROR(AVERAGE(C40:H40),"")</f>
         <v/>
       </c>
-      <c r="J40" s="24" t="n">
-        <v>84.33</v>
-      </c>
+      <c r="J40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -6921,27 +7002,31 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C41" s="28" t="n"/>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D41" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="E41" s="28" t="n"/>
-      <c r="F41" s="28" t="n"/>
+      <c r="E41" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>75</v>
+      </c>
       <c r="G41" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H41" s="29" t="n">
-        <v>92</v>
-      </c>
+      <c r="H41" s="28" t="n"/>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(C41:H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="24" t="n">
-        <v>38.33</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
@@ -6952,20 +7037,28 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
+      <c r="D42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E42" s="28" t="n"/>
       <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
+      <c r="G42" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>92</v>
+      </c>
       <c r="I42" s="22">
         <f>IFERROR(AVERAGE(C42:H42),"")</f>
         <v/>
       </c>
-      <c r="J42" s="28" t="n"/>
+      <c r="J42" s="24" t="n">
+        <v>38.33</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -6975,7 +7068,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -6998,7 +7091,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -7021,14 +7114,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="28" t="n"/>
-      <c r="E45" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="E45" s="28" t="n"/>
       <c r="F45" s="28" t="n"/>
       <c r="G45" s="28" t="n"/>
       <c r="H45" s="28" t="n"/>
@@ -7046,12 +7137,14 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
+      <c r="E46" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F46" s="28" t="n"/>
       <c r="G46" s="28" t="n"/>
       <c r="H46" s="28" t="n"/>
@@ -7069,7 +7162,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -7092,7 +7185,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
@@ -7115,7 +7208,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
@@ -7138,7 +7231,7 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
@@ -7153,8 +7246,31 @@
       </c>
       <c r="J50" s="28" t="n"/>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -7162,9 +7278,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7178,7 +7294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7828,24 +7944,20 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
       <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
-      <c r="J27" s="24" t="n">
-        <v>57.5</v>
-      </c>
+      <c r="J27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -7855,21 +7967,17 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>95</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="23" t="n">
+      <c r="G28" s="23" t="n">
         <v>100</v>
       </c>
+      <c r="H28" s="28" t="n"/>
       <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
@@ -7886,20 +7994,28 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="E29" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
-      <c r="H29" s="28" t="n"/>
+      <c r="H29" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I29" s="22">
         <f>IFERROR(AVERAGE(C29:H29),"")</f>
         <v/>
       </c>
-      <c r="J29" s="28" t="n"/>
+      <c r="J29" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7909,7 +8025,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -7932,7 +8048,7 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
@@ -7955,7 +8071,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -7978,26 +8094,20 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
-      <c r="E33" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
-      <c r="H33" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H33" s="28" t="n"/>
       <c r="I33" s="22">
         <f>IFERROR(AVERAGE(C33:H33),"")</f>
         <v/>
       </c>
-      <c r="J33" s="24" t="n">
-        <v>57.5</v>
-      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -8007,20 +8117,26 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="E34" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
+      <c r="H34" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I34" s="22">
         <f>IFERROR(AVERAGE(C34:H34),"")</f>
         <v/>
       </c>
-      <c r="J34" s="28" t="n"/>
+      <c r="J34" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -8030,13 +8146,11 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
@@ -8045,9 +8159,7 @@
         <f>IFERROR(AVERAGE(C35:H35),"")</f>
         <v/>
       </c>
-      <c r="J35" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -8057,11 +8169,13 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
+      <c r="D36" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
@@ -8070,7 +8184,9 @@
         <f>IFERROR(AVERAGE(C36:H36),"")</f>
         <v/>
       </c>
-      <c r="J36" s="28" t="n"/>
+      <c r="J36" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -8080,7 +8196,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -8103,15 +8219,11 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
-        </is>
-      </c>
-      <c r="C38" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
@@ -8120,9 +8232,7 @@
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
-      <c r="J38" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -8132,23 +8242,25 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="n"/>
-      <c r="G39" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="G39" s="28" t="n"/>
       <c r="H39" s="28" t="n"/>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="24" t="n">
-        <v>57.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
@@ -8159,29 +8271,23 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
+          <t>Madelynn Smith</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
-      <c r="E40" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F40" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
       <c r="G40" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="H40" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H40" s="28" t="n"/>
       <c r="I40" s="22">
         <f>IFERROR(AVERAGE(C40:H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="24" t="n">
-        <v>191.67</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -8192,7 +8298,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
@@ -8203,14 +8309,18 @@
       <c r="F41" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="G41" s="28" t="n"/>
-      <c r="H41" s="28" t="n"/>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(C41:H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="24" t="n">
-        <v>76.67</v>
+        <v>191.67</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
@@ -8221,20 +8331,26 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
+      <c r="E42" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G42" s="28" t="n"/>
       <c r="H42" s="28" t="n"/>
       <c r="I42" s="22">
         <f>IFERROR(AVERAGE(C42:H42),"")</f>
         <v/>
       </c>
-      <c r="J42" s="28" t="n"/>
+      <c r="J42" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -8244,7 +8360,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -8267,7 +8383,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -8290,14 +8406,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="28" t="n"/>
-      <c r="E45" s="30" t="n">
-        <v>80</v>
-      </c>
+      <c r="E45" s="28" t="n"/>
       <c r="F45" s="28" t="n"/>
       <c r="G45" s="28" t="n"/>
       <c r="H45" s="28" t="n"/>
@@ -8315,12 +8429,14 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
+      <c r="E46" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="F46" s="28" t="n"/>
       <c r="G46" s="28" t="n"/>
       <c r="H46" s="28" t="n"/>
@@ -8338,7 +8454,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -8361,7 +8477,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
@@ -8384,7 +8500,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
@@ -8407,13 +8523,11 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
-      <c r="D50" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
       <c r="F50" s="28" t="n"/>
       <c r="G50" s="28" t="n"/>
@@ -8422,12 +8536,37 @@
         <f>IFERROR(AVERAGE(C50:H50),"")</f>
         <v/>
       </c>
-      <c r="J50" s="24" t="n">
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="24" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -8435,9 +8574,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8451,7 +8590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8959,7 +9098,9 @@
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="28" t="n"/>
+      <c r="D21" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="29" t="n">
         <v>95</v>
@@ -9101,14 +9242,12 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="E27" s="28" t="n"/>
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="28" t="n"/>
@@ -9126,14 +9265,14 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
-        </is>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>85</v>
-      </c>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="E28" s="30" t="n">
+        <v>87</v>
+      </c>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="28" t="n"/>
@@ -9151,10 +9290,12 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>85</v>
+      </c>
       <c r="D29" s="28" t="n"/>
       <c r="E29" s="28" t="n"/>
       <c r="F29" s="28" t="n"/>
@@ -9174,7 +9315,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -9182,16 +9323,12 @@
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
-      <c r="H30" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H30" s="28" t="n"/>
       <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="24" t="n">
-        <v>32.86</v>
-      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -9201,7 +9338,7 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
@@ -9209,12 +9346,16 @@
       <c r="E31" s="28" t="n"/>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="28" t="n"/>
+      <c r="H31" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="J31" s="24" t="n">
+        <v>32.86</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -9224,7 +9365,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -9247,13 +9388,11 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
@@ -9272,11 +9411,13 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
+      <c r="D34" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
@@ -9295,7 +9436,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -9318,7 +9459,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -9341,7 +9482,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -9364,7 +9505,7 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
@@ -9372,16 +9513,12 @@
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H38" s="28" t="n"/>
       <c r="I38" s="22">
         <f>IFERROR(AVERAGE(C38:H38),"")</f>
         <v/>
       </c>
-      <c r="J38" s="24" t="n">
-        <v>32.86</v>
-      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -9391,7 +9528,7 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
@@ -9399,12 +9536,16 @@
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="n"/>
       <c r="G39" s="28" t="n"/>
-      <c r="H39" s="28" t="n"/>
+      <c r="H39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="J39" s="24" t="n">
+        <v>32.86</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -9414,30 +9555,20 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
+          <t>Madelynn Smith</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
-      <c r="D40" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
-      <c r="F40" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
       <c r="I40" s="22">
         <f>IFERROR(AVERAGE(C40:H40),"")</f>
         <v/>
       </c>
-      <c r="J40" s="24" t="n">
-        <v>147.86</v>
-      </c>
+      <c r="J40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -9447,20 +9578,30 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
-      <c r="D41" s="28" t="n"/>
+      <c r="D41" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="28" t="n"/>
-      <c r="F41" s="28" t="n"/>
-      <c r="G41" s="28" t="n"/>
-      <c r="H41" s="28" t="n"/>
+      <c r="F41" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(C41:H41),"")</f>
         <v/>
       </c>
-      <c r="J41" s="28" t="n"/>
+      <c r="J41" s="24" t="n">
+        <v>147.86</v>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -9470,7 +9611,7 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
@@ -9493,7 +9634,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -9516,7 +9657,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -9539,7 +9680,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -9562,7 +9703,7 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
@@ -9570,16 +9711,12 @@
       <c r="E46" s="28" t="n"/>
       <c r="F46" s="28" t="n"/>
       <c r="G46" s="28" t="n"/>
-      <c r="H46" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H46" s="28" t="n"/>
       <c r="I46" s="22">
         <f>IFERROR(AVERAGE(C46:H46),"")</f>
         <v/>
       </c>
-      <c r="J46" s="24" t="n">
-        <v>32.86</v>
-      </c>
+      <c r="J46" s="28" t="n"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -9589,7 +9726,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -9597,12 +9734,16 @@
       <c r="E47" s="28" t="n"/>
       <c r="F47" s="28" t="n"/>
       <c r="G47" s="28" t="n"/>
-      <c r="H47" s="28" t="n"/>
+      <c r="H47" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="I47" s="22">
         <f>IFERROR(AVERAGE(C47:H47),"")</f>
         <v/>
       </c>
-      <c r="J47" s="28" t="n"/>
+      <c r="J47" s="24" t="n">
+        <v>32.86</v>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
@@ -9612,7 +9753,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
@@ -9635,7 +9776,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
@@ -9658,29 +9799,52 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="28" t="n"/>
-      <c r="E50" s="30" t="n">
-        <v>87</v>
-      </c>
+      <c r="E50" s="28" t="n"/>
       <c r="F50" s="28" t="n"/>
       <c r="G50" s="28" t="n"/>
-      <c r="H50" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="H50" s="28" t="n"/>
       <c r="I50" s="22">
         <f>IFERROR(AVERAGE(C50:H50),"")</f>
         <v/>
       </c>
-      <c r="J50" s="24" t="n">
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="24" t="n">
         <v>32.86</v>
       </c>
     </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -9688,9 +9852,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9704,7 +9868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10128,7 +10292,7 @@
         <v/>
       </c>
       <c r="J17" s="24" t="n">
-        <v>115</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -10350,22 +10514,26 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="E27" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n"/>
-      <c r="H27" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="G27" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" s="28" t="n"/>
       <c r="I27" s="22">
         <f>IFERROR(AVERAGE(C27:H27),"")</f>
         <v/>
       </c>
-      <c r="J27" s="28" t="n"/>
+      <c r="J27" s="24" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -10375,15 +10543,19 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
+      <c r="D28" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="n"/>
+      <c r="H28" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="I28" s="22">
         <f>IFERROR(AVERAGE(C28:H28),"")</f>
         <v/>
@@ -10398,7 +10570,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
@@ -10421,26 +10593,20 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="n"/>
       <c r="I30" s="22">
         <f>IFERROR(AVERAGE(C30:H30),"")</f>
         <v/>
       </c>
-      <c r="J30" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -10450,20 +10616,26 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
+      <c r="D31" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
+      <c r="F31" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G31" s="28" t="n"/>
       <c r="H31" s="28" t="n"/>
       <c r="I31" s="22">
         <f>IFERROR(AVERAGE(C31:H31),"")</f>
         <v/>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="J31" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -10473,7 +10645,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -10496,7 +10668,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -10519,7 +10691,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -10542,7 +10714,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -10565,7 +10737,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -10588,7 +10760,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -10611,13 +10783,11 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="29" t="n">
-        <v>95</v>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
@@ -10636,24 +10806,22 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
+      <c r="D39" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="E39" s="28" t="n"/>
-      <c r="F39" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F39" s="28" t="n"/>
       <c r="G39" s="28" t="n"/>
       <c r="H39" s="28" t="n"/>
       <c r="I39" s="22">
         <f>IFERROR(AVERAGE(C39:H39),"")</f>
         <v/>
       </c>
-      <c r="J39" s="24" t="n">
-        <v>46</v>
-      </c>
+      <c r="J39" s="28" t="n"/>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -10663,22 +10831,24 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
+          <t>Madelynn Smith</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
-      <c r="E40" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="F40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="G40" s="28" t="n"/>
       <c r="H40" s="28" t="n"/>
       <c r="I40" s="22">
         <f>IFERROR(AVERAGE(C40:H40),"")</f>
         <v/>
       </c>
-      <c r="J40" s="28" t="n"/>
+      <c r="J40" s="24" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -10688,12 +10858,14 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
+          <t>Madison Cureton</t>
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="28" t="n"/>
-      <c r="E41" s="28" t="n"/>
+      <c r="E41" s="29" t="n">
+        <v>95</v>
+      </c>
       <c r="F41" s="28" t="n"/>
       <c r="G41" s="28" t="n"/>
       <c r="H41" s="28" t="n"/>
@@ -10711,7 +10883,7 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
@@ -10734,7 +10906,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -10757,7 +10929,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -10780,7 +10952,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -10803,12 +10975,10 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
       <c r="E46" s="28" t="n"/>
       <c r="F46" s="28" t="n"/>
@@ -10818,9 +10988,7 @@
         <f>IFERROR(AVERAGE(C46:H46),"")</f>
         <v/>
       </c>
-      <c r="J46" s="24" t="n">
-        <v>115</v>
-      </c>
+      <c r="J46" s="28" t="n"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -10830,10 +10998,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="n"/>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D47" s="28" t="n"/>
       <c r="E47" s="28" t="n"/>
       <c r="F47" s="28" t="n"/>
@@ -10843,7 +11013,9 @@
         <f>IFERROR(AVERAGE(C47:H47),"")</f>
         <v/>
       </c>
-      <c r="J47" s="28" t="n"/>
+      <c r="J47" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
@@ -10853,7 +11025,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
@@ -10876,7 +11048,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
@@ -10899,27 +11071,54 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
-      <c r="F50" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="F50" s="28" t="n"/>
       <c r="G50" s="28" t="n"/>
       <c r="H50" s="28" t="n"/>
       <c r="I50" s="22">
         <f>IFERROR(AVERAGE(C50:H50),"")</f>
         <v/>
       </c>
-      <c r="J50" s="24" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="J50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>122.67</v>
+      </c>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -10927,9 +11126,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10943,7 +11142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11463,7 +11662,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Emanuela Kamara</t>
+          <t>Elizabeth Brazell</t>
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
@@ -11483,7 +11682,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Francisco Llorente Mejias</t>
+          <t>Emanuela Kamara</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -11505,12 +11704,14 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Francisco Llorente Mejias</t>
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="E29" s="25" t="n">
+        <v>34</v>
+      </c>
       <c r="F29" s="22">
         <f>IFERROR(AVERAGE(C29:E29),"")</f>
         <v/>
@@ -11525,7 +11726,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Heather Uebelacker-Maddox</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
@@ -11545,7 +11746,7 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Jada Cox</t>
+          <t>Heather Uebelacker-Maddox</t>
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
@@ -11565,7 +11766,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Javeh Goodman</t>
+          <t>Jada Cox</t>
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
@@ -11585,7 +11786,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Jeremiah Matthews</t>
+          <t>Javeh Goodman</t>
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
@@ -11605,7 +11806,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Kable</t>
+          <t>Jeremiah Matthews</t>
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
@@ -11625,7 +11826,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Kaisha Brewer</t>
+          <t>Kable</t>
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
@@ -11645,7 +11846,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Kayla Valenzuela</t>
+          <t>Kaisha Brewer</t>
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
@@ -11665,7 +11866,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Kenzie</t>
+          <t>Kayla Valenzuela</t>
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
@@ -11685,21 +11886,17 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Lidy Henry</t>
+          <t>Kenzie</t>
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="22">
         <f>IFERROR(AVERAGE(C38:E38),"")</f>
         <v/>
       </c>
-      <c r="G38" s="24" t="n">
-        <v>57.5</v>
-      </c>
+      <c r="G38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -11709,17 +11906,21 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Madelynn Smith</t>
+          <t>Lidy Henry</t>
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
+      <c r="D39" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="22">
         <f>IFERROR(AVERAGE(C39:E39),"")</f>
         <v/>
       </c>
-      <c r="G39" s="28" t="n"/>
+      <c r="G39" s="24" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -11729,21 +11930,17 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Madison Cureton</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>100</v>
-      </c>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
       <c r="F40" s="22">
         <f>IFERROR(AVERAGE(C40:E40),"")</f>
         <v/>
       </c>
-      <c r="G40" s="24" t="n">
-        <v>230</v>
-      </c>
+      <c r="G40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -11753,17 +11950,21 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Maylin Hernandez Rodriguez</t>
-        </is>
-      </c>
-      <c r="C41" s="28" t="n"/>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="D41" s="28" t="n"/>
       <c r="E41" s="28" t="n"/>
       <c r="F41" s="22">
         <f>IFERROR(AVERAGE(C41:E41),"")</f>
         <v/>
       </c>
-      <c r="G41" s="28" t="n"/>
+      <c r="G41" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -11773,7 +11974,7 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maylin Hernandez Rodriguez</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
@@ -11793,7 +11994,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Mykenize Milledge</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
@@ -11813,7 +12014,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Nyatiek Keah</t>
+          <t>Mykenize Milledge</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -11833,7 +12034,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Richard Gibbs</t>
+          <t>Nyatiek Keah</t>
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
@@ -11853,7 +12054,7 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>Rusul Kadhim</t>
+          <t>Richard Gibbs</t>
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
@@ -11873,7 +12074,7 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Rusul Kadhim</t>
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
@@ -11893,7 +12094,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Samuel Galban Rocha</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
@@ -11913,7 +12114,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Serina Gaskins</t>
+          <t>Samuel Galban Rocha</t>
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
@@ -11933,24 +12134,46 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>Zack Whitten</t>
+          <t>Serina Gaskins</t>
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
-      <c r="D50" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
       <c r="F50" s="22">
         <f>IFERROR(AVERAGE(C50:E50),"")</f>
         <v/>
       </c>
-      <c r="G50" s="24" t="n">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="G50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="22">
+        <f>IFERROR(AVERAGE(C51:E51),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="24" t="n">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
         </is>
@@ -11958,9 +12181,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -11142,7 +11142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11150,8 +11150,9 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -11181,10 +11182,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 4</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -11212,8 +11218,13 @@
           <t>09/23</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>09/25</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -11237,8 +11248,13 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -11256,8 +11272,11 @@
       <c r="E5" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
+      <c r="F5" s="12" t="n">
+        <v>43</v>
+      </c>
       <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -11271,6 +11290,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -11284,6 +11304,7 @@
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -11297,6 +11318,7 @@
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -11310,6 +11332,7 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -11323,6 +11346,7 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -11333,12 +11357,13 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -11360,11 +11385,12 @@
         <v>100</v>
       </c>
       <c r="E12" s="21" t="n"/>
-      <c r="F12" s="22">
-        <f>IFERROR(AVERAGE(C12:E12),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="24" t="n">
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="22">
+        <f>IFERROR(AVERAGE(C12:F12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="24" t="n">
         <v>57.5</v>
       </c>
     </row>
@@ -11382,11 +11408,12 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="22">
-        <f>IFERROR(AVERAGE(C13:E13),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="22">
+        <f>IFERROR(AVERAGE(C13:F13),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -11402,11 +11429,12 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="22">
-        <f>IFERROR(AVERAGE(C14:E14),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="22">
+        <f>IFERROR(AVERAGE(C14:F14),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -11422,11 +11450,12 @@
       <c r="C15" s="21" t="n"/>
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="21" t="n"/>
-      <c r="F15" s="22">
-        <f>IFERROR(AVERAGE(C15:E15),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="22">
+        <f>IFERROR(AVERAGE(C15:F15),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -11444,11 +11473,14 @@
       <c r="E16" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="F16" s="22">
-        <f>IFERROR(AVERAGE(C16:E16),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="28" t="n"/>
+      <c r="F16" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="G16" s="22">
+        <f>IFERROR(AVERAGE(C16:F16),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -11464,11 +11496,12 @@
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="22">
-        <f>IFERROR(AVERAGE(C17:E17),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="22">
+        <f>IFERROR(AVERAGE(C17:F17),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="28" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -11484,11 +11517,12 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="22">
-        <f>IFERROR(AVERAGE(C18:E18),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="22">
+        <f>IFERROR(AVERAGE(C18:F18),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -11504,11 +11538,12 @@
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="22">
-        <f>IFERROR(AVERAGE(C19:E19),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="22">
+        <f>IFERROR(AVERAGE(C19:F19),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -11524,11 +11559,12 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="22">
-        <f>IFERROR(AVERAGE(C20:E20),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="22">
+        <f>IFERROR(AVERAGE(C20:F20),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -11544,11 +11580,12 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="22">
-        <f>IFERROR(AVERAGE(C21:E21),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="22">
+        <f>IFERROR(AVERAGE(C21:F21),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -11566,11 +11603,12 @@
         <v>100</v>
       </c>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="22">
-        <f>IFERROR(AVERAGE(C22:E22),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="24" t="n">
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="22">
+        <f>IFERROR(AVERAGE(C22:F22),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="24" t="n">
         <v>57.5</v>
       </c>
     </row>
@@ -11588,11 +11626,12 @@
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="22">
-        <f>IFERROR(AVERAGE(C23:E23),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="28" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="22">
+        <f>IFERROR(AVERAGE(C23:F23),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -11608,11 +11647,12 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
-      <c r="F24" s="22">
-        <f>IFERROR(AVERAGE(C24:E24),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="22">
+        <f>IFERROR(AVERAGE(C24:F24),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -11628,11 +11668,12 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="22">
-        <f>IFERROR(AVERAGE(C25:E25),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="22">
+        <f>IFERROR(AVERAGE(C25:F25),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -11648,11 +11689,12 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="22">
-        <f>IFERROR(AVERAGE(C26:E26),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="22">
+        <f>IFERROR(AVERAGE(C26:F26),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -11668,11 +11710,14 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
-      <c r="F27" s="22">
-        <f>IFERROR(AVERAGE(C27:E27),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="28" t="n"/>
+      <c r="F27" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" s="22">
+        <f>IFERROR(AVERAGE(C27:F27),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -11690,11 +11735,12 @@
       <c r="E28" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="F28" s="22">
-        <f>IFERROR(AVERAGE(C28:E28),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="22">
+        <f>IFERROR(AVERAGE(C28:F28),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -11712,11 +11758,12 @@
       <c r="E29" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="F29" s="22">
-        <f>IFERROR(AVERAGE(C29:E29),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="22">
+        <f>IFERROR(AVERAGE(C29:F29),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -11732,11 +11779,12 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="22">
-        <f>IFERROR(AVERAGE(C30:E30),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="22">
+        <f>IFERROR(AVERAGE(C30:F30),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -11752,11 +11800,12 @@
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="22">
-        <f>IFERROR(AVERAGE(C31:E31),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="22">
+        <f>IFERROR(AVERAGE(C31:F31),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -11772,11 +11821,12 @@
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="22">
-        <f>IFERROR(AVERAGE(C32:E32),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="22">
+        <f>IFERROR(AVERAGE(C32:F32),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -11792,11 +11842,12 @@
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="22">
-        <f>IFERROR(AVERAGE(C33:E33),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="22">
+        <f>IFERROR(AVERAGE(C33:F33),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -11812,11 +11863,12 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="22">
-        <f>IFERROR(AVERAGE(C34:E34),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="22">
+        <f>IFERROR(AVERAGE(C34:F34),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -11832,11 +11884,12 @@
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
-      <c r="F35" s="22">
-        <f>IFERROR(AVERAGE(C35:E35),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="22">
+        <f>IFERROR(AVERAGE(C35:F35),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -11852,11 +11905,12 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="22">
-        <f>IFERROR(AVERAGE(C36:E36),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="22">
+        <f>IFERROR(AVERAGE(C36:F36),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -11872,11 +11926,12 @@
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="22">
-        <f>IFERROR(AVERAGE(C37:E37),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="22">
+        <f>IFERROR(AVERAGE(C37:F37),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -11892,11 +11947,12 @@
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="22">
-        <f>IFERROR(AVERAGE(C38:E38),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="22">
+        <f>IFERROR(AVERAGE(C38:F38),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -11914,11 +11970,12 @@
         <v>100</v>
       </c>
       <c r="E39" s="28" t="n"/>
-      <c r="F39" s="22">
-        <f>IFERROR(AVERAGE(C39:E39),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="24" t="n">
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="22">
+        <f>IFERROR(AVERAGE(C39:F39),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="24" t="n">
         <v>57.5</v>
       </c>
     </row>
@@ -11936,11 +11993,12 @@
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
-      <c r="F40" s="22">
-        <f>IFERROR(AVERAGE(C40:E40),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="22">
+        <f>IFERROR(AVERAGE(C40:F40),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -11958,11 +12016,14 @@
       </c>
       <c r="D41" s="28" t="n"/>
       <c r="E41" s="28" t="n"/>
-      <c r="F41" s="22">
-        <f>IFERROR(AVERAGE(C41:E41),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="24" t="n">
+      <c r="F41" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="G41" s="22">
+        <f>IFERROR(AVERAGE(C41:F41),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="24" t="n">
         <v>115</v>
       </c>
     </row>
@@ -11980,11 +12041,12 @@
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="28" t="n"/>
       <c r="E42" s="28" t="n"/>
-      <c r="F42" s="22">
-        <f>IFERROR(AVERAGE(C42:E42),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="22">
+        <f>IFERROR(AVERAGE(C42:F42),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="28" t="n"/>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -12000,11 +12062,12 @@
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="28" t="n"/>
       <c r="E43" s="28" t="n"/>
-      <c r="F43" s="22">
-        <f>IFERROR(AVERAGE(C43:E43),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="22">
+        <f>IFERROR(AVERAGE(C43:F43),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="28" t="n"/>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
@@ -12020,11 +12083,12 @@
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="28" t="n"/>
       <c r="E44" s="28" t="n"/>
-      <c r="F44" s="22">
-        <f>IFERROR(AVERAGE(C44:E44),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="22">
+        <f>IFERROR(AVERAGE(C44:F44),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="28" t="n"/>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
@@ -12040,11 +12104,12 @@
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="28" t="n"/>
       <c r="E45" s="28" t="n"/>
-      <c r="F45" s="22">
-        <f>IFERROR(AVERAGE(C45:E45),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="22">
+        <f>IFERROR(AVERAGE(C45:F45),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="28" t="n"/>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
@@ -12060,11 +12125,12 @@
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
       <c r="E46" s="28" t="n"/>
-      <c r="F46" s="22">
-        <f>IFERROR(AVERAGE(C46:E46),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="22">
+        <f>IFERROR(AVERAGE(C46:F46),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="28" t="n"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -12080,11 +12146,12 @@
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="28" t="n"/>
       <c r="E47" s="28" t="n"/>
-      <c r="F47" s="22">
-        <f>IFERROR(AVERAGE(C47:E47),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="22">
+        <f>IFERROR(AVERAGE(C47:F47),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="28" t="n"/>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
@@ -12100,11 +12167,12 @@
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
-      <c r="F48" s="22">
-        <f>IFERROR(AVERAGE(C48:E48),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="22">
+        <f>IFERROR(AVERAGE(C48:F48),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="28" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -12120,11 +12188,12 @@
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="28" t="n"/>
       <c r="E49" s="28" t="n"/>
-      <c r="F49" s="22">
-        <f>IFERROR(AVERAGE(C49:E49),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="22">
+        <f>IFERROR(AVERAGE(C49:F49),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="28" t="n"/>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -12140,11 +12209,12 @@
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
-      <c r="F50" s="22">
-        <f>IFERROR(AVERAGE(C50:E50),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="22">
+        <f>IFERROR(AVERAGE(C50:F50),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="28" t="n"/>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
@@ -12164,11 +12234,12 @@
         <v>100</v>
       </c>
       <c r="E51" s="28" t="n"/>
-      <c r="F51" s="22">
-        <f>IFERROR(AVERAGE(C51:E51),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="24" t="n">
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="22">
+        <f>IFERROR(AVERAGE(C51:F51),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="24" t="n">
         <v>172.5</v>
       </c>
     </row>
@@ -12182,8 +12253,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -16,6 +16,7 @@
     <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="October" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2165,6 +2166,905 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECRET SHOPPER SCORES — OCTOBER 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>10/04</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Meal Period</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SCORE</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Enthusiasm</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Return</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Likely to Recommend</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Exceptional Act?</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>INDIVIDUAL PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MTD SCORE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>MTD DOLLARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Robert Cline</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22">
+        <f>IFERROR(AVERAGE(C12:C12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Vicki Lucey</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22">
+        <f>IFERROR(AVERAGE(C13:C13),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Kasey Wilson</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22">
+        <f>IFERROR(AVERAGE(C14:C14),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Nathan Roberts</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22">
+        <f>IFERROR(AVERAGE(C15:C15),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Ailen Gonzalez Cardero</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="22">
+        <f>IFERROR(AVERAGE(C16:C16),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Anthony Pirtle</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="22">
+        <f>IFERROR(AVERAGE(C17:C17),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="22">
+        <f>IFERROR(AVERAGE(C18:C18),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Autumn Hearn</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="22">
+        <f>IFERROR(AVERAGE(C19:C19),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Brianna Gatewood</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="22">
+        <f>IFERROR(AVERAGE(C20:C20),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Christopher Conder</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="22">
+        <f>IFERROR(AVERAGE(C21:C21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Cortez Brown</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="22">
+        <f>IFERROR(AVERAGE(C22:C22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>DJuan Johnson</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="22">
+        <f>IFERROR(AVERAGE(C23:C23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>DaKayla Dorsey</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="22">
+        <f>IFERROR(AVERAGE(C24:C24),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Damon</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="22">
+        <f>IFERROR(AVERAGE(C25:C25),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Divan</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="22">
+        <f>IFERROR(AVERAGE(C26:C26),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Elizabeth Brazell</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="22">
+        <f>IFERROR(AVERAGE(C27:C27),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Emanuela Kamara</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="D28" s="22">
+        <f>IFERROR(AVERAGE(C28:C28),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Francisco Llorente Mejias</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="22">
+        <f>IFERROR(AVERAGE(C29:C29),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="22">
+        <f>IFERROR(AVERAGE(C30:C30),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Heather Uebelacker-Maddox</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="22">
+        <f>IFERROR(AVERAGE(C31:C31),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Jada Cox</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="22">
+        <f>IFERROR(AVERAGE(C32:C32),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Javeh Goodman</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="22">
+        <f>IFERROR(AVERAGE(C33:C33),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Jeremiah Matthews</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="22">
+        <f>IFERROR(AVERAGE(C34:C34),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Kable</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="22">
+        <f>IFERROR(AVERAGE(C35:C35),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Kaisha Brewer</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="22">
+        <f>IFERROR(AVERAGE(C36:C36),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Kayla Valenzuela</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="22">
+        <f>IFERROR(AVERAGE(C37:C37),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Kenzie</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="22">
+        <f>IFERROR(AVERAGE(C38:C38),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Lidy Henry</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="22">
+        <f>IFERROR(AVERAGE(C39:C39),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Madelynn Smith</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="22">
+        <f>IFERROR(AVERAGE(C40:C40),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="28" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Madison Cureton</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="22">
+        <f>IFERROR(AVERAGE(C41:C41),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Maylin Hernandez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="22">
+        <f>IFERROR(AVERAGE(C42:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="22">
+        <f>IFERROR(AVERAGE(C43:C43),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Mykenize Milledge</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="22">
+        <f>IFERROR(AVERAGE(C44:C44),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Nyatiek Keah</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="22">
+        <f>IFERROR(AVERAGE(C45:C45),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Richard Gibbs</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="22">
+        <f>IFERROR(AVERAGE(C46:C46),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Rusul Kadhim</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="22">
+        <f>IFERROR(AVERAGE(C47:C47),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="22">
+        <f>IFERROR(AVERAGE(C48:C48),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Samuel Galban Rocha</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="22">
+        <f>IFERROR(AVERAGE(C49:C49),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Serina Gaskins</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="22">
+        <f>IFERROR(AVERAGE(C50:C50),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Zack Whitten</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="22">
+        <f>IFERROR(AVERAGE(C51:C51),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>Score = shop score if on shift during meal window; blank if not. MTD SCORE = average of scores worked. MTD DOLLARS = $230 ÷ on-shift count per 100% shop.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:B11"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -2172,14 +2172,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2199,10 +2201,20 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -2220,8 +2232,18 @@
           <t>10/04</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -2235,8 +2257,18 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -2248,8 +2280,14 @@
       <c r="C5" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="D5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -2261,6 +2299,8 @@
       <c r="C6" s="17" t="n"/>
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -2272,6 +2312,8 @@
       <c r="C7" s="17" t="n"/>
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -2283,6 +2325,8 @@
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -2294,6 +2338,8 @@
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -2305,6 +2351,8 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -2313,12 +2361,14 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -2336,11 +2386,15 @@
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="22">
-        <f>IFERROR(AVERAGE(C12:C12),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" s="22">
+        <f>IFERROR(AVERAGE(C12:E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -2354,11 +2408,13 @@
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
-      <c r="D13" s="22">
-        <f>IFERROR(AVERAGE(C13:C13),"")</f>
-        <v/>
-      </c>
+      <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
+      <c r="F13" s="22">
+        <f>IFERROR(AVERAGE(C13:E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -2372,11 +2428,13 @@
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="22">
-        <f>IFERROR(AVERAGE(C14:C14),"")</f>
-        <v/>
-      </c>
+      <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
+      <c r="F14" s="22">
+        <f>IFERROR(AVERAGE(C14:E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -2390,11 +2448,13 @@
         </is>
       </c>
       <c r="C15" s="21" t="n"/>
-      <c r="D15" s="22">
-        <f>IFERROR(AVERAGE(C15:C15),"")</f>
-        <v/>
-      </c>
+      <c r="D15" s="21" t="n"/>
       <c r="E15" s="21" t="n"/>
+      <c r="F15" s="22">
+        <f>IFERROR(AVERAGE(C15:E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -2408,11 +2468,13 @@
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
-      <c r="D16" s="22">
-        <f>IFERROR(AVERAGE(C16:C16),"")</f>
-        <v/>
-      </c>
+      <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
+      <c r="F16" s="22">
+        <f>IFERROR(AVERAGE(C16:E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -2426,11 +2488,17 @@
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
-      <c r="D17" s="22">
-        <f>IFERROR(AVERAGE(C17:C17),"")</f>
-        <v/>
+      <c r="D17" s="23" t="n">
+        <v>100</v>
       </c>
       <c r="E17" s="28" t="n"/>
+      <c r="F17" s="22">
+        <f>IFERROR(AVERAGE(C17:E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -2444,11 +2512,13 @@
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
-      <c r="D18" s="22">
-        <f>IFERROR(AVERAGE(C18:C18),"")</f>
-        <v/>
-      </c>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
+      <c r="F18" s="22">
+        <f>IFERROR(AVERAGE(C18:E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -2462,11 +2532,13 @@
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="22">
-        <f>IFERROR(AVERAGE(C19:C19),"")</f>
-        <v/>
-      </c>
+      <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
+      <c r="F19" s="22">
+        <f>IFERROR(AVERAGE(C19:E19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -2480,11 +2552,13 @@
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="22">
-        <f>IFERROR(AVERAGE(C20:C20),"")</f>
-        <v/>
-      </c>
+      <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
+      <c r="F20" s="22">
+        <f>IFERROR(AVERAGE(C20:E20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -2498,11 +2572,13 @@
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="22">
-        <f>IFERROR(AVERAGE(C21:C21),"")</f>
-        <v/>
-      </c>
+      <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
+      <c r="F21" s="22">
+        <f>IFERROR(AVERAGE(C21:E21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -2516,11 +2592,13 @@
         </is>
       </c>
       <c r="C22" s="28" t="n"/>
-      <c r="D22" s="22">
-        <f>IFERROR(AVERAGE(C22:C22),"")</f>
-        <v/>
-      </c>
+      <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
+      <c r="F22" s="22">
+        <f>IFERROR(AVERAGE(C22:E22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -2534,11 +2612,13 @@
         </is>
       </c>
       <c r="C23" s="28" t="n"/>
-      <c r="D23" s="22">
-        <f>IFERROR(AVERAGE(C23:C23),"")</f>
-        <v/>
-      </c>
+      <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
+      <c r="F23" s="22">
+        <f>IFERROR(AVERAGE(C23:E23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -2552,11 +2632,13 @@
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
-      <c r="D24" s="22">
-        <f>IFERROR(AVERAGE(C24:C24),"")</f>
-        <v/>
-      </c>
+      <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
+      <c r="F24" s="22">
+        <f>IFERROR(AVERAGE(C24:E24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -2570,11 +2652,13 @@
         </is>
       </c>
       <c r="C25" s="28" t="n"/>
-      <c r="D25" s="22">
-        <f>IFERROR(AVERAGE(C25:C25),"")</f>
-        <v/>
-      </c>
+      <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
+      <c r="F25" s="22">
+        <f>IFERROR(AVERAGE(C25:E25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -2588,11 +2672,13 @@
         </is>
       </c>
       <c r="C26" s="28" t="n"/>
-      <c r="D26" s="22">
-        <f>IFERROR(AVERAGE(C26:C26),"")</f>
-        <v/>
-      </c>
+      <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
+      <c r="F26" s="22">
+        <f>IFERROR(AVERAGE(C26:E26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -2606,11 +2692,13 @@
         </is>
       </c>
       <c r="C27" s="28" t="n"/>
-      <c r="D27" s="22">
-        <f>IFERROR(AVERAGE(C27:C27),"")</f>
-        <v/>
-      </c>
+      <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
+      <c r="F27" s="22">
+        <f>IFERROR(AVERAGE(C27:E27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -2626,11 +2714,13 @@
       <c r="C28" s="29" t="n">
         <v>92</v>
       </c>
-      <c r="D28" s="22">
-        <f>IFERROR(AVERAGE(C28:C28),"")</f>
-        <v/>
-      </c>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
+      <c r="F28" s="22">
+        <f>IFERROR(AVERAGE(C28:E28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -2644,11 +2734,15 @@
         </is>
       </c>
       <c r="C29" s="28" t="n"/>
-      <c r="D29" s="22">
-        <f>IFERROR(AVERAGE(C29:C29),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F29" s="22">
+        <f>IFERROR(AVERAGE(C29:E29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -2662,11 +2756,13 @@
         </is>
       </c>
       <c r="C30" s="28" t="n"/>
-      <c r="D30" s="22">
-        <f>IFERROR(AVERAGE(C30:C30),"")</f>
-        <v/>
-      </c>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
+      <c r="F30" s="22">
+        <f>IFERROR(AVERAGE(C30:E30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -2680,11 +2776,13 @@
         </is>
       </c>
       <c r="C31" s="28" t="n"/>
-      <c r="D31" s="22">
-        <f>IFERROR(AVERAGE(C31:C31),"")</f>
-        <v/>
-      </c>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
+      <c r="F31" s="22">
+        <f>IFERROR(AVERAGE(C31:E31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -2698,11 +2796,13 @@
         </is>
       </c>
       <c r="C32" s="28" t="n"/>
-      <c r="D32" s="22">
-        <f>IFERROR(AVERAGE(C32:C32),"")</f>
-        <v/>
-      </c>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
+      <c r="F32" s="22">
+        <f>IFERROR(AVERAGE(C32:E32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -2716,11 +2816,13 @@
         </is>
       </c>
       <c r="C33" s="28" t="n"/>
-      <c r="D33" s="22">
-        <f>IFERROR(AVERAGE(C33:C33),"")</f>
-        <v/>
-      </c>
+      <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
+      <c r="F33" s="22">
+        <f>IFERROR(AVERAGE(C33:E33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -2734,11 +2836,13 @@
         </is>
       </c>
       <c r="C34" s="28" t="n"/>
-      <c r="D34" s="22">
-        <f>IFERROR(AVERAGE(C34:C34),"")</f>
-        <v/>
-      </c>
+      <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
+      <c r="F34" s="22">
+        <f>IFERROR(AVERAGE(C34:E34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -2752,11 +2856,13 @@
         </is>
       </c>
       <c r="C35" s="28" t="n"/>
-      <c r="D35" s="22">
-        <f>IFERROR(AVERAGE(C35:C35),"")</f>
-        <v/>
-      </c>
+      <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
+      <c r="F35" s="22">
+        <f>IFERROR(AVERAGE(C35:E35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -2770,11 +2876,13 @@
         </is>
       </c>
       <c r="C36" s="28" t="n"/>
-      <c r="D36" s="22">
-        <f>IFERROR(AVERAGE(C36:C36),"")</f>
-        <v/>
-      </c>
+      <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
+      <c r="F36" s="22">
+        <f>IFERROR(AVERAGE(C36:E36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -2788,11 +2896,13 @@
         </is>
       </c>
       <c r="C37" s="28" t="n"/>
-      <c r="D37" s="22">
-        <f>IFERROR(AVERAGE(C37:C37),"")</f>
-        <v/>
-      </c>
+      <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
+      <c r="F37" s="22">
+        <f>IFERROR(AVERAGE(C37:E37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -2806,11 +2916,13 @@
         </is>
       </c>
       <c r="C38" s="28" t="n"/>
-      <c r="D38" s="22">
-        <f>IFERROR(AVERAGE(C38:C38),"")</f>
-        <v/>
-      </c>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
+      <c r="F38" s="22">
+        <f>IFERROR(AVERAGE(C38:E38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -2824,11 +2936,13 @@
         </is>
       </c>
       <c r="C39" s="28" t="n"/>
-      <c r="D39" s="22">
-        <f>IFERROR(AVERAGE(C39:C39),"")</f>
-        <v/>
-      </c>
+      <c r="D39" s="28" t="n"/>
       <c r="E39" s="28" t="n"/>
+      <c r="F39" s="22">
+        <f>IFERROR(AVERAGE(C39:E39),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="28" t="n"/>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -2842,11 +2956,15 @@
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
-      <c r="D40" s="22">
-        <f>IFERROR(AVERAGE(C40:C40),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F40" s="22">
+        <f>IFERROR(AVERAGE(C40:E40),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="28" t="n"/>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -2860,11 +2978,13 @@
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
-      <c r="D41" s="22">
-        <f>IFERROR(AVERAGE(C41:C41),"")</f>
-        <v/>
-      </c>
+      <c r="D41" s="28" t="n"/>
       <c r="E41" s="28" t="n"/>
+      <c r="F41" s="22">
+        <f>IFERROR(AVERAGE(C41:E41),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="28" t="n"/>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -2878,11 +2998,13 @@
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
-      <c r="D42" s="22">
-        <f>IFERROR(AVERAGE(C42:C42),"")</f>
-        <v/>
-      </c>
+      <c r="D42" s="28" t="n"/>
       <c r="E42" s="28" t="n"/>
+      <c r="F42" s="22">
+        <f>IFERROR(AVERAGE(C42:E42),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="28" t="n"/>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -2896,11 +3018,13 @@
         </is>
       </c>
       <c r="C43" s="28" t="n"/>
-      <c r="D43" s="22">
-        <f>IFERROR(AVERAGE(C43:C43),"")</f>
-        <v/>
-      </c>
+      <c r="D43" s="28" t="n"/>
       <c r="E43" s="28" t="n"/>
+      <c r="F43" s="22">
+        <f>IFERROR(AVERAGE(C43:E43),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="28" t="n"/>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
@@ -2914,11 +3038,13 @@
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
-      <c r="D44" s="22">
-        <f>IFERROR(AVERAGE(C44:C44),"")</f>
-        <v/>
-      </c>
+      <c r="D44" s="28" t="n"/>
       <c r="E44" s="28" t="n"/>
+      <c r="F44" s="22">
+        <f>IFERROR(AVERAGE(C44:E44),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="28" t="n"/>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
@@ -2932,11 +3058,13 @@
         </is>
       </c>
       <c r="C45" s="28" t="n"/>
-      <c r="D45" s="22">
-        <f>IFERROR(AVERAGE(C45:C45),"")</f>
-        <v/>
-      </c>
+      <c r="D45" s="28" t="n"/>
       <c r="E45" s="28" t="n"/>
+      <c r="F45" s="22">
+        <f>IFERROR(AVERAGE(C45:E45),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="28" t="n"/>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
@@ -2950,11 +3078,13 @@
         </is>
       </c>
       <c r="C46" s="28" t="n"/>
-      <c r="D46" s="22">
-        <f>IFERROR(AVERAGE(C46:C46),"")</f>
-        <v/>
-      </c>
+      <c r="D46" s="28" t="n"/>
       <c r="E46" s="28" t="n"/>
+      <c r="F46" s="22">
+        <f>IFERROR(AVERAGE(C46:E46),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="28" t="n"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -2968,11 +3098,17 @@
         </is>
       </c>
       <c r="C47" s="28" t="n"/>
-      <c r="D47" s="22">
-        <f>IFERROR(AVERAGE(C47:C47),"")</f>
-        <v/>
+      <c r="D47" s="23" t="n">
+        <v>100</v>
       </c>
       <c r="E47" s="28" t="n"/>
+      <c r="F47" s="22">
+        <f>IFERROR(AVERAGE(C47:E47),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="24" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
@@ -2986,11 +3122,13 @@
         </is>
       </c>
       <c r="C48" s="28" t="n"/>
-      <c r="D48" s="22">
-        <f>IFERROR(AVERAGE(C48:C48),"")</f>
-        <v/>
-      </c>
+      <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
+      <c r="F48" s="22">
+        <f>IFERROR(AVERAGE(C48:E48),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="28" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -3004,11 +3142,13 @@
         </is>
       </c>
       <c r="C49" s="28" t="n"/>
-      <c r="D49" s="22">
-        <f>IFERROR(AVERAGE(C49:C49),"")</f>
-        <v/>
-      </c>
+      <c r="D49" s="28" t="n"/>
       <c r="E49" s="28" t="n"/>
+      <c r="F49" s="22">
+        <f>IFERROR(AVERAGE(C49:E49),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="28" t="n"/>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -3022,11 +3162,13 @@
         </is>
       </c>
       <c r="C50" s="28" t="n"/>
-      <c r="D50" s="22">
-        <f>IFERROR(AVERAGE(C50:C50),"")</f>
-        <v/>
-      </c>
+      <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
+      <c r="F50" s="22">
+        <f>IFERROR(AVERAGE(C50:E50),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="28" t="n"/>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
@@ -3040,11 +3182,15 @@
         </is>
       </c>
       <c r="C51" s="28" t="n"/>
-      <c r="D51" s="22">
-        <f>IFERROR(AVERAGE(C51:C51),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F51" s="22">
+        <f>IFERROR(AVERAGE(C51:E51),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="28" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1">
       <c r="A52" s="31" t="inlineStr">
@@ -3055,9 +3201,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="October" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="October" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="October" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="October" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -2172,7 +2172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2180,8 +2180,11 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2211,10 +2214,25 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>WEEK 4</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 5</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WEEK 6</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -2242,8 +2260,23 @@
           <t>10/12</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr"/>
@@ -2267,8 +2300,23 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
@@ -2286,8 +2334,17 @@
       <c r="E5" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
+      <c r="F5" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="15" t="inlineStr"/>
@@ -2301,6 +2358,9 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="15" t="inlineStr"/>
@@ -2314,6 +2374,9 @@
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="15" t="inlineStr"/>
@@ -2327,6 +2390,9 @@
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="15" t="inlineStr"/>
@@ -2340,6 +2406,9 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="15" t="inlineStr"/>
@@ -2353,6 +2422,9 @@
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -2363,12 +2435,15 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>MTD SCORE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>MTD DOLLARS</t>
         </is>
@@ -2390,11 +2465,14 @@
       <c r="E12" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="F12" s="22">
-        <f>IFERROR(AVERAGE(C12:E12),"")</f>
-        <v/>
-      </c>
+      <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="22">
+        <f>IFERROR(AVERAGE(C12:H12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -2410,11 +2488,18 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
-      <c r="F13" s="22">
-        <f>IFERROR(AVERAGE(C13:E13),"")</f>
-        <v/>
-      </c>
+      <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
+      <c r="H13" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="22">
+        <f>IFERROR(AVERAGE(C13:H13),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -2430,11 +2515,14 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="F14" s="22">
-        <f>IFERROR(AVERAGE(C14:E14),"")</f>
-        <v/>
-      </c>
+      <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -2450,11 +2538,14 @@
       <c r="C15" s="21" t="n"/>
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="21" t="n"/>
-      <c r="F15" s="22">
-        <f>IFERROR(AVERAGE(C15:E15),"")</f>
-        <v/>
-      </c>
+      <c r="F15" s="21" t="n"/>
       <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22">
+        <f>IFERROR(AVERAGE(C15:H15),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -2470,11 +2561,14 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
-      <c r="F16" s="22">
-        <f>IFERROR(AVERAGE(C16:E16),"")</f>
-        <v/>
-      </c>
+      <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="22">
+        <f>IFERROR(AVERAGE(C16:H16),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="28" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -2492,11 +2586,14 @@
         <v>100</v>
       </c>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="22">
-        <f>IFERROR(AVERAGE(C17:E17),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="24" t="n">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="22">
+        <f>IFERROR(AVERAGE(C17:H17),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="24" t="n">
         <v>115</v>
       </c>
     </row>
@@ -2514,11 +2611,14 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="22">
-        <f>IFERROR(AVERAGE(C18:E18),"")</f>
-        <v/>
-      </c>
+      <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="22">
+        <f>IFERROR(AVERAGE(C18:H18),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -2534,11 +2634,14 @@
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="22">
-        <f>IFERROR(AVERAGE(C19:E19),"")</f>
-        <v/>
-      </c>
+      <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="22">
+        <f>IFERROR(AVERAGE(C19:H19),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="28" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -2554,11 +2657,14 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="22">
-        <f>IFERROR(AVERAGE(C20:E20),"")</f>
-        <v/>
-      </c>
+      <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="22">
+        <f>IFERROR(AVERAGE(C20:H20),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="28" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -2574,11 +2680,14 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="28" t="n"/>
       <c r="E21" s="28" t="n"/>
-      <c r="F21" s="22">
-        <f>IFERROR(AVERAGE(C21:E21),"")</f>
-        <v/>
-      </c>
+      <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="22">
+        <f>IFERROR(AVERAGE(C21:H21),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="28" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -2594,11 +2703,14 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
-      <c r="F22" s="22">
-        <f>IFERROR(AVERAGE(C22:E22),"")</f>
-        <v/>
-      </c>
+      <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="22">
+        <f>IFERROR(AVERAGE(C22:H22),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="28" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -2614,11 +2726,14 @@
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="28" t="n"/>
-      <c r="F23" s="22">
-        <f>IFERROR(AVERAGE(C23:E23),"")</f>
-        <v/>
-      </c>
+      <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="22">
+        <f>IFERROR(AVERAGE(C23:H23),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="28" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -2634,11 +2749,14 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
-      <c r="F24" s="22">
-        <f>IFERROR(AVERAGE(C24:E24),"")</f>
-        <v/>
-      </c>
+      <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="22">
+        <f>IFERROR(AVERAGE(C24:H24),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="28" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -2654,11 +2772,14 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="28" t="n"/>
       <c r="E25" s="28" t="n"/>
-      <c r="F25" s="22">
-        <f>IFERROR(AVERAGE(C25:E25),"")</f>
-        <v/>
-      </c>
+      <c r="F25" s="28" t="n"/>
       <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="22">
+        <f>IFERROR(AVERAGE(C25:H25),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="28" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -2674,11 +2795,14 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
-      <c r="F26" s="22">
-        <f>IFERROR(AVERAGE(C26:E26),"")</f>
-        <v/>
-      </c>
+      <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="22">
+        <f>IFERROR(AVERAGE(C26:H26),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="28" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -2694,11 +2818,14 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="n"/>
       <c r="E27" s="28" t="n"/>
-      <c r="F27" s="22">
-        <f>IFERROR(AVERAGE(C27:E27),"")</f>
-        <v/>
-      </c>
+      <c r="F27" s="28" t="n"/>
       <c r="G27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="22">
+        <f>IFERROR(AVERAGE(C27:H27),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="28" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -2716,11 +2843,14 @@
       </c>
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
-      <c r="F28" s="22">
-        <f>IFERROR(AVERAGE(C28:E28),"")</f>
-        <v/>
-      </c>
+      <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="22">
+        <f>IFERROR(AVERAGE(C28:H28),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -2738,11 +2868,14 @@
       <c r="E29" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="F29" s="22">
-        <f>IFERROR(AVERAGE(C29:E29),"")</f>
-        <v/>
-      </c>
+      <c r="F29" s="28" t="n"/>
       <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="22">
+        <f>IFERROR(AVERAGE(C29:H29),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="28" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -2758,11 +2891,14 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
-      <c r="F30" s="22">
-        <f>IFERROR(AVERAGE(C30:E30),"")</f>
-        <v/>
-      </c>
+      <c r="F30" s="28" t="n"/>
       <c r="G30" s="28" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="22">
+        <f>IFERROR(AVERAGE(C30:H30),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="28" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -2778,11 +2914,14 @@
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
-      <c r="F31" s="22">
-        <f>IFERROR(AVERAGE(C31:E31),"")</f>
-        <v/>
-      </c>
+      <c r="F31" s="28" t="n"/>
       <c r="G31" s="28" t="n"/>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="22">
+        <f>IFERROR(AVERAGE(C31:H31),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="28" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
@@ -2798,11 +2937,14 @@
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
-      <c r="F32" s="22">
-        <f>IFERROR(AVERAGE(C32:E32),"")</f>
-        <v/>
-      </c>
+      <c r="F32" s="28" t="n"/>
       <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="22">
+        <f>IFERROR(AVERAGE(C32:H32),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="28" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -2818,11 +2960,14 @@
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="n"/>
       <c r="E33" s="28" t="n"/>
-      <c r="F33" s="22">
-        <f>IFERROR(AVERAGE(C33:E33),"")</f>
-        <v/>
-      </c>
+      <c r="F33" s="28" t="n"/>
       <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="22">
+        <f>IFERROR(AVERAGE(C33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -2838,11 +2983,14 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
-      <c r="F34" s="22">
-        <f>IFERROR(AVERAGE(C34:E34),"")</f>
-        <v/>
-      </c>
+      <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="22">
+        <f>IFERROR(AVERAGE(C34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="28" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
@@ -2858,11 +3006,14 @@
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="28" t="n"/>
       <c r="E35" s="28" t="n"/>
-      <c r="F35" s="22">
-        <f>IFERROR(AVERAGE(C35:E35),"")</f>
-        <v/>
-      </c>
+      <c r="F35" s="28" t="n"/>
       <c r="G35" s="28" t="n"/>
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="22">
+        <f>IFERROR(AVERAGE(C35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="28" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
@@ -2878,11 +3029,14 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
-      <c r="F36" s="22">
-        <f>IFERROR(AVERAGE(C36:E36),"")</f>
-        <v/>
-      </c>
+      <c r="F36" s="28" t="n"/>
       <c r="G36" s="28" t="n"/>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="22">
+        <f>IFERROR(AVERAGE(C36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="28" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
@@ -2898,11 +3052,14 @@
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="28" t="n"/>
       <c r="E37" s="28" t="n"/>
-      <c r="F37" s="22">
-        <f>IFERROR(AVERAGE(C37:E37),"")</f>
-        <v/>
-      </c>
+      <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="22">
+        <f>IFERROR(AVERAGE(C37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="28" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
@@ -2918,11 +3075,14 @@
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
-      <c r="F38" s="22">
-        <f>IFERROR(AVERAGE(C38:E38),"")</f>
-        <v/>
-      </c>
+      <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="22">
+        <f>IFERROR(AVERAGE(C38:H38),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="28" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -2938,11 +3098,18 @@
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="28" t="n"/>
       <c r="E39" s="28" t="n"/>
-      <c r="F39" s="22">
-        <f>IFERROR(AVERAGE(C39:E39),"")</f>
-        <v/>
-      </c>
+      <c r="F39" s="28" t="n"/>
       <c r="G39" s="28" t="n"/>
+      <c r="H39" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="22">
+        <f>IFERROR(AVERAGE(C39:H39),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
@@ -2960,11 +3127,18 @@
       <c r="E40" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="F40" s="22">
-        <f>IFERROR(AVERAGE(C40:E40),"")</f>
-        <v/>
-      </c>
+      <c r="F40" s="28" t="n"/>
       <c r="G40" s="28" t="n"/>
+      <c r="H40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="22">
+        <f>IFERROR(AVERAGE(C40:H40),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -2980,11 +3154,16 @@
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="28" t="n"/>
       <c r="E41" s="28" t="n"/>
-      <c r="F41" s="22">
-        <f>IFERROR(AVERAGE(C41:E41),"")</f>
-        <v/>
+      <c r="F41" s="29" t="n">
+        <v>92</v>
       </c>
       <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="22">
+        <f>IFERROR(AVERAGE(C41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="28" t="n"/>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -3000,11 +3179,14 @@
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="28" t="n"/>
       <c r="E42" s="28" t="n"/>
-      <c r="F42" s="22">
-        <f>IFERROR(AVERAGE(C42:E42),"")</f>
-        <v/>
-      </c>
+      <c r="F42" s="28" t="n"/>
       <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="22">
+        <f>IFERROR(AVERAGE(C42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="28" t="n"/>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -3020,11 +3202,14 @@
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="28" t="n"/>
       <c r="E43" s="28" t="n"/>
-      <c r="F43" s="22">
-        <f>IFERROR(AVERAGE(C43:E43),"")</f>
-        <v/>
-      </c>
+      <c r="F43" s="28" t="n"/>
       <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="22">
+        <f>IFERROR(AVERAGE(C43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="28" t="n"/>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
@@ -3040,11 +3225,14 @@
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="28" t="n"/>
       <c r="E44" s="28" t="n"/>
-      <c r="F44" s="22">
-        <f>IFERROR(AVERAGE(C44:E44),"")</f>
-        <v/>
-      </c>
+      <c r="F44" s="28" t="n"/>
       <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="22">
+        <f>IFERROR(AVERAGE(C44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="28" t="n"/>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
@@ -3060,11 +3248,14 @@
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="28" t="n"/>
       <c r="E45" s="28" t="n"/>
-      <c r="F45" s="22">
-        <f>IFERROR(AVERAGE(C45:E45),"")</f>
-        <v/>
-      </c>
+      <c r="F45" s="28" t="n"/>
       <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="22">
+        <f>IFERROR(AVERAGE(C45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="28" t="n"/>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
@@ -3080,11 +3271,14 @@
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
       <c r="E46" s="28" t="n"/>
-      <c r="F46" s="22">
-        <f>IFERROR(AVERAGE(C46:E46),"")</f>
-        <v/>
-      </c>
+      <c r="F46" s="28" t="n"/>
       <c r="G46" s="28" t="n"/>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="22">
+        <f>IFERROR(AVERAGE(C46:H46),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="28" t="n"/>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
@@ -3102,11 +3296,14 @@
         <v>100</v>
       </c>
       <c r="E47" s="28" t="n"/>
-      <c r="F47" s="22">
-        <f>IFERROR(AVERAGE(C47:E47),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="24" t="n">
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="22">
+        <f>IFERROR(AVERAGE(C47:H47),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="24" t="n">
         <v>115</v>
       </c>
     </row>
@@ -3124,11 +3321,14 @@
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
-      <c r="F48" s="22">
-        <f>IFERROR(AVERAGE(C48:E48),"")</f>
-        <v/>
-      </c>
+      <c r="F48" s="28" t="n"/>
       <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="22">
+        <f>IFERROR(AVERAGE(C48:H48),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="28" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -3144,11 +3344,14 @@
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="28" t="n"/>
       <c r="E49" s="28" t="n"/>
-      <c r="F49" s="22">
-        <f>IFERROR(AVERAGE(C49:E49),"")</f>
-        <v/>
-      </c>
+      <c r="F49" s="28" t="n"/>
       <c r="G49" s="28" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="22">
+        <f>IFERROR(AVERAGE(C49:H49),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="28" t="n"/>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -3164,11 +3367,14 @@
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
-      <c r="F50" s="22">
-        <f>IFERROR(AVERAGE(C50:E50),"")</f>
-        <v/>
-      </c>
+      <c r="F50" s="28" t="n"/>
       <c r="G50" s="28" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="22">
+        <f>IFERROR(AVERAGE(C50:H50),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="28" t="n"/>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
@@ -3186,11 +3392,14 @@
       <c r="E51" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="F51" s="22">
-        <f>IFERROR(AVERAGE(C51:E51),"")</f>
-        <v/>
-      </c>
+      <c r="F51" s="28" t="n"/>
       <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="22">
+        <f>IFERROR(AVERAGE(C51:H51),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="28" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1">
       <c r="A52" s="31" t="inlineStr">
@@ -3201,9 +3410,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Shop_Tracker_2065_2026.xlsx
+++ b/Shop_Tracker_2065_2026.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="January" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="April" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="June" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="July" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="October" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1 Summary" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2 Summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3 Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4 Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="January" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="April" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="May" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="June" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="July" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="August" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="September" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="October" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Q1 Summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Q2 Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Q3 Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Q4 Summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
